--- a/data/VM-konk Drammen.xlsx
+++ b/data/VM-konk Drammen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erlin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakon\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A40269-C4EE-4B76-B486-865DF12F5289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA67614-A9E6-487F-A5C5-CE19EDD0C0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E8AE97E4-6608-4AF7-A972-B11E82B68E07}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{E8AE97E4-6608-4AF7-A972-B11E82B68E07}"/>
   </bookViews>
   <sheets>
     <sheet name="Gruppespill" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -64,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="172">
   <si>
     <t>Gruppe A</t>
   </si>
@@ -591,6 +588,21 @@
   </si>
   <si>
     <t>Nr.</t>
+  </si>
+  <si>
+    <t>Tor Arne</t>
+  </si>
+  <si>
+    <t>Harry Kane</t>
+  </si>
+  <si>
+    <t>Antonio Nusa</t>
+  </si>
+  <si>
+    <t>Khalid Al-Turais</t>
+  </si>
+  <si>
+    <t>Arne Scheie</t>
   </si>
 </sst>
 </file>
@@ -678,7 +690,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,6 +736,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -909,7 +927,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1111,6 +1129,53 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1183,25 +1248,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="21" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1209,15 +1256,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1851,7 +1889,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2167,91 +2205,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0E5F76-7D89-4DB9-881E-721C49B5536A}">
-  <dimension ref="B1:AC121"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:AG121"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="47" customWidth="1"/>
-    <col min="2" max="2" width="7.109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.88671875" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" style="49" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.88671875" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.5546875" style="47" customWidth="1"/>
-    <col min="8" max="8" width="1.44140625" style="47" customWidth="1"/>
-    <col min="9" max="9" width="3.5546875" style="47" customWidth="1"/>
-    <col min="10" max="10" width="3.109375" style="47" customWidth="1"/>
-    <col min="11" max="11" width="1.44140625" style="47" customWidth="1"/>
-    <col min="12" max="12" width="3.109375" style="47" customWidth="1"/>
-    <col min="13" max="13" width="2.88671875" style="47" customWidth="1"/>
-    <col min="14" max="14" width="3.109375" style="47" customWidth="1"/>
-    <col min="15" max="15" width="1.44140625" style="47" customWidth="1"/>
-    <col min="16" max="16" width="3.109375" style="47" customWidth="1"/>
-    <col min="17" max="17" width="2.88671875" style="47" customWidth="1"/>
-    <col min="18" max="18" width="3.109375" style="47" customWidth="1"/>
-    <col min="19" max="19" width="1.44140625" style="47" customWidth="1"/>
-    <col min="20" max="20" width="3.109375" style="47" customWidth="1"/>
-    <col min="21" max="21" width="2.88671875" style="47" customWidth="1"/>
-    <col min="22" max="22" width="3.109375" style="47" customWidth="1"/>
-    <col min="23" max="23" width="1.44140625" style="47" customWidth="1"/>
-    <col min="24" max="24" width="3.109375" style="47" customWidth="1"/>
-    <col min="25" max="25" width="2.88671875" style="47" customWidth="1"/>
-    <col min="26" max="26" width="3.109375" style="47" customWidth="1"/>
-    <col min="27" max="27" width="1.44140625" style="47" customWidth="1"/>
-    <col min="28" max="28" width="3.109375" style="47" customWidth="1"/>
-    <col min="29" max="29" width="2.88671875" style="47" customWidth="1"/>
-    <col min="30" max="16384" width="11.44140625" style="47"/>
+    <col min="2" max="2" width="7.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" style="49" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" style="47" customWidth="1"/>
+    <col min="8" max="8" width="1.42578125" style="47" customWidth="1"/>
+    <col min="9" max="9" width="3.5703125" style="47" customWidth="1"/>
+    <col min="10" max="10" width="3.140625" style="47" customWidth="1"/>
+    <col min="11" max="11" width="1.42578125" style="47" customWidth="1"/>
+    <col min="12" max="12" width="3.140625" style="47" customWidth="1"/>
+    <col min="13" max="13" width="2.85546875" style="47" customWidth="1"/>
+    <col min="14" max="14" width="3.140625" style="47" customWidth="1"/>
+    <col min="15" max="15" width="1.42578125" style="47" customWidth="1"/>
+    <col min="16" max="16" width="3.140625" style="47" customWidth="1"/>
+    <col min="17" max="17" width="2.85546875" style="47" customWidth="1"/>
+    <col min="18" max="18" width="3.140625" style="47" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="47" customWidth="1"/>
+    <col min="20" max="20" width="3.140625" style="47" customWidth="1"/>
+    <col min="21" max="21" width="2.85546875" style="47" customWidth="1"/>
+    <col min="22" max="22" width="3.140625" style="47" customWidth="1"/>
+    <col min="23" max="23" width="1.42578125" style="47" customWidth="1"/>
+    <col min="24" max="24" width="3.140625" style="47" customWidth="1"/>
+    <col min="25" max="25" width="2.85546875" style="47" customWidth="1"/>
+    <col min="26" max="26" width="3.140625" style="47" customWidth="1"/>
+    <col min="27" max="27" width="1.42578125" style="47" customWidth="1"/>
+    <col min="28" max="28" width="3.140625" style="47" customWidth="1"/>
+    <col min="29" max="29" width="2.85546875" style="47" customWidth="1"/>
+    <col min="30" max="30" width="3.140625" style="47" customWidth="1"/>
+    <col min="31" max="31" width="1.42578125" style="47" customWidth="1"/>
+    <col min="32" max="32" width="3.140625" style="47" customWidth="1"/>
+    <col min="33" max="33" width="2.85546875" style="47" customWidth="1"/>
+    <col min="34" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C2" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="84"/>
-      <c r="F2" s="85"/>
+      <c r="D2" s="102" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="103"/>
+      <c r="F2" s="104"/>
       <c r="G2" s="72" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="73"/>
       <c r="I2" s="74"/>
-      <c r="J2" s="89" t="s">
+      <c r="J2" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="92" t="s">
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="111" t="s">
         <v>139</v>
       </c>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-      <c r="Q2" s="94"/>
-      <c r="R2" s="98" t="s">
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="100"/>
-      <c r="V2" s="101" t="s">
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
+      <c r="U2" s="119"/>
+      <c r="V2" s="120" t="s">
         <v>140</v>
       </c>
-      <c r="W2" s="102"/>
-      <c r="X2" s="102"/>
-      <c r="Y2" s="103"/>
-      <c r="Z2" s="95" t="s">
+      <c r="W2" s="121"/>
+      <c r="X2" s="121"/>
+      <c r="Y2" s="122"/>
+      <c r="Z2" s="114" t="s">
         <v>138</v>
       </c>
-      <c r="AA2" s="96"/>
-      <c r="AB2" s="96"/>
-      <c r="AC2" s="97"/>
-    </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AA2" s="115"/>
+      <c r="AB2" s="115"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="99" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE2" s="100"/>
+      <c r="AF2" s="100"/>
+      <c r="AG2" s="101"/>
+    </row>
+    <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="12">
         <v>46184</v>
       </c>
@@ -2333,8 +2381,21 @@
         <f>IF(ISBLANK($I3)=TRUE,"",IF(SIGN(Z3-AB3)=SIGN($G3-$I3),1,0)+IF(Z3=$G3,IF(AB3=$I3,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD3" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="11" t="str">
+        <f>IF(ISBLANK($I3)=TRUE,"",IF(SIGN(AD3-AF3)=SIGN($G3-$I3),1,0)+IF(AD3=$G3,IF(AF3=$I3,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="12">
         <v>46185</v>
       </c>
@@ -2416,8 +2477,21 @@
         <f t="shared" ref="AC4:AC8" si="4">IF(ISBLANK($G4)=TRUE,"",IF(SIGN(Z4-AB4)=SIGN($G4-$I4),1,0)+IF(Z4=$G4,IF(AB4=$I4,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="9" t="str">
+        <f t="shared" ref="AG4:AG8" si="5">IF(ISBLANK($G4)=TRUE,"",IF(SIGN(AD4-AF4)=SIGN($G4-$I4),1,0)+IF(AD4=$G4,IF(AF4=$I4,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="12">
         <v>46191</v>
       </c>
@@ -2499,8 +2573,21 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="12">
         <v>46192</v>
       </c>
@@ -2582,8 +2669,21 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD6" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="12">
         <v>46198</v>
       </c>
@@ -2665,8 +2765,21 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="8" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG7" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="13">
         <v>46198</v>
       </c>
@@ -2748,19 +2861,32 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="9" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="8">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="84"/>
-      <c r="F9" s="85"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="104"/>
       <c r="G9" s="72" t="s">
         <v>7</v>
       </c>
@@ -2786,8 +2912,12 @@
       <c r="AA9" s="51"/>
       <c r="AB9" s="51"/>
       <c r="AC9" s="52"/>
-    </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD9" s="83"/>
+      <c r="AE9" s="84"/>
+      <c r="AF9" s="84"/>
+      <c r="AG9" s="85"/>
+    </row>
+    <row r="10" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="12">
         <v>46185</v>
       </c>
@@ -2869,8 +2999,21 @@
         <f>IF(ISBLANK($I10)=TRUE,"",IF(SIGN(Z10-AB10)=SIGN($G10-$I10),1,0)+IF(Z10=$G10,IF(AB10=$I10,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="11" t="str">
+        <f>IF(ISBLANK($I10)=TRUE,"",IF(SIGN(AD10-AF10)=SIGN($G10-$I10),1,0)+IF(AD10=$G10,IF(AF10=$I10,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="12">
         <v>46186</v>
       </c>
@@ -2901,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="9" t="str">
-        <f t="shared" ref="M11:M15" si="5">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(J11-L11)=SIGN($G11-$I11),1,0)+IF(J11=$G11,IF(L11=$I11,2,0),0))</f>
+        <f t="shared" ref="M11:M15" si="6">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(J11-L11)=SIGN($G11-$I11),1,0)+IF(J11=$G11,IF(L11=$I11,2,0),0))</f>
         <v/>
       </c>
       <c r="N11" s="3">
@@ -2914,7 +3057,7 @@
         <v>2</v>
       </c>
       <c r="Q11" s="9" t="str">
-        <f t="shared" ref="Q11:Q15" si="6">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(N11-P11)=SIGN($G11-$I11),1,0)+IF(N11=$G11,IF(P11=$I11,2,0),0))</f>
+        <f t="shared" ref="Q11:Q15" si="7">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(N11-P11)=SIGN($G11-$I11),1,0)+IF(N11=$G11,IF(P11=$I11,2,0),0))</f>
         <v/>
       </c>
       <c r="R11" s="3">
@@ -2927,7 +3070,7 @@
         <v>2</v>
       </c>
       <c r="U11" s="9" t="str">
-        <f t="shared" ref="U11:U15" si="7">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(R11-T11)=SIGN($G11-$I11),1,0)+IF(R11=$G11,IF(T11=$I11,2,0),0))</f>
+        <f t="shared" ref="U11:U15" si="8">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(R11-T11)=SIGN($G11-$I11),1,0)+IF(R11=$G11,IF(T11=$I11,2,0),0))</f>
         <v/>
       </c>
       <c r="V11" s="3"/>
@@ -2936,7 +3079,7 @@
       </c>
       <c r="X11" s="7"/>
       <c r="Y11" s="9" t="str">
-        <f t="shared" ref="Y11:Y15" si="8">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(V11-X11)=SIGN($G11-$I11),1,0)+IF(V11=$G11,IF(X11=$I11,2,0),0))</f>
+        <f t="shared" ref="Y11:Y15" si="9">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(V11-X11)=SIGN($G11-$I11),1,0)+IF(V11=$G11,IF(X11=$I11,2,0),0))</f>
         <v/>
       </c>
       <c r="Z11" s="3">
@@ -2949,11 +3092,24 @@
         <v>3</v>
       </c>
       <c r="AC11" s="9" t="str">
-        <f t="shared" ref="AC11:AC15" si="9">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(Z11-AB11)=SIGN($G11-$I11),1,0)+IF(Z11=$G11,IF(AB11=$I11,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC11:AC15" si="10">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(Z11-AB11)=SIGN($G11-$I11),1,0)+IF(Z11=$G11,IF(AB11=$I11,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG11" s="9" t="str">
+        <f t="shared" ref="AG11:AG15" si="11">IF(ISBLANK($G11)=TRUE,"",IF(SIGN(AD11-AF11)=SIGN($G11-$I11),1,0)+IF(AD11=$G11,IF(AF11=$I11,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="12">
         <v>46191</v>
       </c>
@@ -2984,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N12" s="3">
@@ -2997,7 +3153,7 @@
         <v>1</v>
       </c>
       <c r="Q12" s="9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R12" s="3">
@@ -3010,7 +3166,7 @@
         <v>1</v>
       </c>
       <c r="U12" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="V12" s="3"/>
@@ -3019,7 +3175,7 @@
       </c>
       <c r="X12" s="7"/>
       <c r="Y12" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Z12" s="3">
@@ -3032,11 +3188,24 @@
         <v>0</v>
       </c>
       <c r="AC12" s="9" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AD12" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="9" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>46192</v>
       </c>
@@ -3067,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N13" s="3">
@@ -3080,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R13" s="3">
@@ -3093,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="U13" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="V13" s="3"/>
@@ -3102,7 +3271,7 @@
       </c>
       <c r="X13" s="7"/>
       <c r="Y13" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Z13" s="3">
@@ -3115,11 +3284,24 @@
         <v>1</v>
       </c>
       <c r="AC13" s="9" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AD13" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="9" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="12">
         <v>46197</v>
       </c>
@@ -3150,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N14" s="3">
@@ -3163,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="Q14" s="9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R14" s="3">
@@ -3176,7 +3358,7 @@
         <v>1</v>
       </c>
       <c r="U14" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="V14" s="3"/>
@@ -3185,7 +3367,7 @@
       </c>
       <c r="X14" s="7"/>
       <c r="Y14" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Z14" s="3">
@@ -3198,11 +3380,24 @@
         <v>0</v>
       </c>
       <c r="AC14" s="9" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AD14" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="9" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="13">
         <v>46197</v>
       </c>
@@ -3233,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N15" s="4">
@@ -3246,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R15" s="4">
@@ -3259,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="U15" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="V15" s="4"/>
@@ -3268,7 +3463,7 @@
       </c>
       <c r="X15" s="8"/>
       <c r="Y15" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Z15" s="4">
@@ -3281,22 +3476,35 @@
         <v>4</v>
       </c>
       <c r="AC15" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AD15" s="4">
+        <v>2</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="10" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C16" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="83" t="s">
+      <c r="D16" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="84"/>
-      <c r="F16" s="85"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="104"/>
       <c r="G16" s="72" t="s">
         <v>7</v>
       </c>
@@ -3322,8 +3530,12 @@
       <c r="AA16" s="51"/>
       <c r="AB16" s="51"/>
       <c r="AC16" s="52"/>
-    </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD16" s="83"/>
+      <c r="AE16" s="84"/>
+      <c r="AF16" s="84"/>
+      <c r="AG16" s="85"/>
+    </row>
+    <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="12">
         <v>46187</v>
       </c>
@@ -3405,8 +3617,21 @@
         <f>IF(ISBLANK($I17)=TRUE,"",IF(SIGN(Z17-AB17)=SIGN($G17-$I17),1,0)+IF(Z17=$G17,IF(AB17=$I17,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG17" s="11" t="str">
+        <f>IF(ISBLANK($I17)=TRUE,"",IF(SIGN(AD17-AF17)=SIGN($G17-$I17),1,0)+IF(AD17=$G17,IF(AF17=$I17,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="12">
         <v>46187</v>
       </c>
@@ -3437,7 +3662,7 @@
         <v>2</v>
       </c>
       <c r="M18" s="9" t="str">
-        <f t="shared" ref="M18:M22" si="10">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(J18-L18)=SIGN($G18-$I18),1,0)+IF(J18=$G18,IF(L18=$I18,2,0),0))</f>
+        <f t="shared" ref="M18:M22" si="12">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(J18-L18)=SIGN($G18-$I18),1,0)+IF(J18=$G18,IF(L18=$I18,2,0),0))</f>
         <v/>
       </c>
       <c r="N18" s="3">
@@ -3450,7 +3675,7 @@
         <v>3</v>
       </c>
       <c r="Q18" s="9" t="str">
-        <f t="shared" ref="Q18:Q22" si="11">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(N18-P18)=SIGN($G18-$I18),1,0)+IF(N18=$G18,IF(P18=$I18,2,0),0))</f>
+        <f t="shared" ref="Q18:Q22" si="13">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(N18-P18)=SIGN($G18-$I18),1,0)+IF(N18=$G18,IF(P18=$I18,2,0),0))</f>
         <v/>
       </c>
       <c r="R18" s="3">
@@ -3463,7 +3688,7 @@
         <v>4</v>
       </c>
       <c r="U18" s="9" t="str">
-        <f t="shared" ref="U18:U22" si="12">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(R18-T18)=SIGN($G18-$I18),1,0)+IF(R18=$G18,IF(T18=$I18,2,0),0))</f>
+        <f t="shared" ref="U18:U22" si="14">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(R18-T18)=SIGN($G18-$I18),1,0)+IF(R18=$G18,IF(T18=$I18,2,0),0))</f>
         <v/>
       </c>
       <c r="V18" s="3"/>
@@ -3472,7 +3697,7 @@
       </c>
       <c r="X18" s="7"/>
       <c r="Y18" s="9" t="str">
-        <f t="shared" ref="Y18:Y22" si="13">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(V18-X18)=SIGN($G18-$I18),1,0)+IF(V18=$G18,IF(X18=$I18,2,0),0))</f>
+        <f t="shared" ref="Y18:Y22" si="15">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(V18-X18)=SIGN($G18-$I18),1,0)+IF(V18=$G18,IF(X18=$I18,2,0),0))</f>
         <v/>
       </c>
       <c r="Z18" s="3">
@@ -3485,11 +3710,24 @@
         <v>3</v>
       </c>
       <c r="AC18" s="9" t="str">
-        <f t="shared" ref="AC18:AC22" si="14">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(Z18-AB18)=SIGN($G18-$I18),1,0)+IF(Z18=$G18,IF(AB18=$I18,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC18:AC22" si="16">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(Z18-AB18)=SIGN($G18-$I18),1,0)+IF(Z18=$G18,IF(AB18=$I18,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="9" t="str">
+        <f t="shared" ref="AG18:AG22" si="17">IF(ISBLANK($G18)=TRUE,"",IF(SIGN(AD18-AF18)=SIGN($G18-$I18),1,0)+IF(AD18=$G18,IF(AF18=$I18,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="12">
         <v>46193</v>
       </c>
@@ -3520,7 +3758,7 @@
         <v>1</v>
       </c>
       <c r="M19" s="9" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="N19" s="3">
@@ -3533,7 +3771,7 @@
         <v>2</v>
       </c>
       <c r="Q19" s="9" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R19" s="3">
@@ -3546,7 +3784,7 @@
         <v>2</v>
       </c>
       <c r="U19" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="V19" s="3"/>
@@ -3555,7 +3793,7 @@
       </c>
       <c r="X19" s="7"/>
       <c r="Y19" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="Z19" s="3">
@@ -3568,11 +3806,24 @@
         <v>2</v>
       </c>
       <c r="AC19" s="9" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="AD19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="7">
+        <v>3</v>
+      </c>
+      <c r="AG19" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="12">
         <v>46193</v>
       </c>
@@ -3603,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="9" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="N20" s="3">
@@ -3616,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="9" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R20" s="3">
@@ -3629,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="U20" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="V20" s="3"/>
@@ -3638,7 +3889,7 @@
       </c>
       <c r="X20" s="7"/>
       <c r="Y20" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="Z20" s="3">
@@ -3651,11 +3902,24 @@
         <v>0</v>
       </c>
       <c r="AC20" s="9" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="AD20" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="12">
         <v>46198</v>
       </c>
@@ -3686,7 +3950,7 @@
         <v>2</v>
       </c>
       <c r="M21" s="9" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="N21" s="3">
@@ -3699,7 +3963,7 @@
         <v>2</v>
       </c>
       <c r="Q21" s="9" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R21" s="3">
@@ -3712,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="U21" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="V21" s="3"/>
@@ -3721,7 +3985,7 @@
       </c>
       <c r="X21" s="7"/>
       <c r="Y21" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="Z21" s="3">
@@ -3734,11 +3998,24 @@
         <v>3</v>
       </c>
       <c r="AC21" s="9" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="AD21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="7">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="13">
         <v>46198</v>
       </c>
@@ -3769,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="N22" s="4">
@@ -3782,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="Q22" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R22" s="4">
@@ -3795,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="V22" s="4"/>
@@ -3804,7 +4081,7 @@
       </c>
       <c r="X22" s="8"/>
       <c r="Y22" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="Z22" s="4">
@@ -3817,22 +4094,35 @@
         <v>1</v>
       </c>
       <c r="AC22" s="10" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="AD22" s="4">
+        <v>3</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C23" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="83" t="s">
+      <c r="D23" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="84"/>
-      <c r="F23" s="85"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="104"/>
       <c r="G23" s="72" t="s">
         <v>7</v>
       </c>
@@ -3858,8 +4148,12 @@
       <c r="AA23" s="51"/>
       <c r="AB23" s="51"/>
       <c r="AC23" s="52"/>
-    </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD23" s="83"/>
+      <c r="AE23" s="84"/>
+      <c r="AF23" s="84"/>
+      <c r="AG23" s="85"/>
+    </row>
+    <row r="24" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" s="12">
         <v>46186</v>
       </c>
@@ -3941,8 +4235,21 @@
         <f>IF(ISBLANK($I24)=TRUE,"",IF(SIGN(Z24-AB24)=SIGN($G24-$I24),1,0)+IF(Z24=$G24,IF(AB24=$I24,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD24" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="11" t="str">
+        <f>IF(ISBLANK($I24)=TRUE,"",IF(SIGN(AD24-AF24)=SIGN($G24-$I24),1,0)+IF(AD24=$G24,IF(AF24=$I24,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" s="12">
         <v>46187</v>
       </c>
@@ -3973,7 +4280,7 @@
         <v>2</v>
       </c>
       <c r="M25" s="9" t="str">
-        <f t="shared" ref="M25:M29" si="15">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(J25-L25)=SIGN($G25-$I25),1,0)+IF(J25=$G25,IF(L25=$I25,2,0),0))</f>
+        <f t="shared" ref="M25:M29" si="18">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(J25-L25)=SIGN($G25-$I25),1,0)+IF(J25=$G25,IF(L25=$I25,2,0),0))</f>
         <v/>
       </c>
       <c r="N25" s="3">
@@ -3986,7 +4293,7 @@
         <v>2</v>
       </c>
       <c r="Q25" s="9" t="str">
-        <f t="shared" ref="Q25:Q29" si="16">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(N25-P25)=SIGN($G25-$I25),1,0)+IF(N25=$G25,IF(P25=$I25,2,0),0))</f>
+        <f t="shared" ref="Q25:Q29" si="19">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(N25-P25)=SIGN($G25-$I25),1,0)+IF(N25=$G25,IF(P25=$I25,2,0),0))</f>
         <v/>
       </c>
       <c r="R25" s="3">
@@ -3999,7 +4306,7 @@
         <v>1</v>
       </c>
       <c r="U25" s="9" t="str">
-        <f t="shared" ref="U25:U29" si="17">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(R25-T25)=SIGN($G25-$I25),1,0)+IF(R25=$G25,IF(T25=$I25,2,0),0))</f>
+        <f t="shared" ref="U25:U29" si="20">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(R25-T25)=SIGN($G25-$I25),1,0)+IF(R25=$G25,IF(T25=$I25,2,0),0))</f>
         <v/>
       </c>
       <c r="V25" s="3"/>
@@ -4008,7 +4315,7 @@
       </c>
       <c r="X25" s="7"/>
       <c r="Y25" s="9" t="str">
-        <f t="shared" ref="Y25:Y29" si="18">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(V25-X25)=SIGN($G25-$I25),1,0)+IF(V25=$G25,IF(X25=$I25,2,0),0))</f>
+        <f t="shared" ref="Y25:Y29" si="21">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(V25-X25)=SIGN($G25-$I25),1,0)+IF(V25=$G25,IF(X25=$I25,2,0),0))</f>
         <v/>
       </c>
       <c r="Z25" s="3">
@@ -4021,11 +4328,24 @@
         <v>0</v>
       </c>
       <c r="AC25" s="9" t="str">
-        <f t="shared" ref="AC25:AC29" si="19">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(Z25-AB25)=SIGN($G25-$I25),1,0)+IF(Z25=$G25,IF(AB25=$I25,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC25:AC29" si="22">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(Z25-AB25)=SIGN($G25-$I25),1,0)+IF(Z25=$G25,IF(AB25=$I25,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG25" s="9" t="str">
+        <f t="shared" ref="AG25:AG29" si="23">IF(ISBLANK($G25)=TRUE,"",IF(SIGN(AD25-AF25)=SIGN($G25-$I25),1,0)+IF(AD25=$G25,IF(AF25=$I25,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" s="12">
         <v>46192</v>
       </c>
@@ -4056,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N26" s="3">
@@ -4069,7 +4389,7 @@
         <v>1</v>
       </c>
       <c r="Q26" s="9" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R26" s="3">
@@ -4082,7 +4402,7 @@
         <v>0</v>
       </c>
       <c r="U26" s="9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="V26" s="3"/>
@@ -4091,7 +4411,7 @@
       </c>
       <c r="X26" s="7"/>
       <c r="Y26" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z26" s="3">
@@ -4104,11 +4424,24 @@
         <v>2</v>
       </c>
       <c r="AC26" s="9" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AD26" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF26" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="9" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" s="12">
         <v>46193</v>
       </c>
@@ -4139,7 +4472,7 @@
         <v>1</v>
       </c>
       <c r="M27" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N27" s="3">
@@ -4152,7 +4485,7 @@
         <v>1</v>
       </c>
       <c r="Q27" s="9" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R27" s="3">
@@ -4165,7 +4498,7 @@
         <v>2</v>
       </c>
       <c r="U27" s="9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="V27" s="3"/>
@@ -4174,7 +4507,7 @@
       </c>
       <c r="X27" s="7"/>
       <c r="Y27" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z27" s="3">
@@ -4187,11 +4520,24 @@
         <v>3</v>
       </c>
       <c r="AC27" s="9" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AD27" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG27" s="9" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" s="12">
         <v>46199</v>
       </c>
@@ -4222,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="M28" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N28" s="3">
@@ -4235,7 +4581,7 @@
         <v>1</v>
       </c>
       <c r="Q28" s="9" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R28" s="3">
@@ -4248,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="U28" s="9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="V28" s="3"/>
@@ -4257,7 +4603,7 @@
       </c>
       <c r="X28" s="7"/>
       <c r="Y28" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z28" s="3">
@@ -4270,11 +4616,24 @@
         <v>3</v>
       </c>
       <c r="AC28" s="9" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AD28" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF28" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG28" s="9" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="13">
         <v>46199</v>
       </c>
@@ -4305,7 +4664,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N29" s="4">
@@ -4318,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="Q29" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R29" s="4">
@@ -4331,7 +4690,7 @@
         <v>1</v>
       </c>
       <c r="U29" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="V29" s="4"/>
@@ -4340,7 +4699,7 @@
       </c>
       <c r="X29" s="8"/>
       <c r="Y29" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z29" s="4">
@@ -4353,22 +4712,35 @@
         <v>1</v>
       </c>
       <c r="AC29" s="10" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AD29" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF29" s="8">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="10" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C30" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="83" t="s">
+      <c r="D30" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="84"/>
-      <c r="F30" s="85"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="104"/>
       <c r="G30" s="72" t="s">
         <v>7</v>
       </c>
@@ -4394,8 +4766,12 @@
       <c r="AA30" s="51"/>
       <c r="AB30" s="51"/>
       <c r="AC30" s="52"/>
-    </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD30" s="83"/>
+      <c r="AE30" s="84"/>
+      <c r="AF30" s="84"/>
+      <c r="AG30" s="85"/>
+    </row>
+    <row r="31" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B31" s="12">
         <v>46187</v>
       </c>
@@ -4477,8 +4853,21 @@
         <f>IF(ISBLANK($I31)=TRUE,"",IF(SIGN(Z31-AB31)=SIGN($G31-$I31),1,0)+IF(Z31=$G31,IF(AB31=$I31,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD31" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="11" t="str">
+        <f>IF(ISBLANK($I31)=TRUE,"",IF(SIGN(AD31-AF31)=SIGN($G31-$I31),1,0)+IF(AD31=$G31,IF(AF31=$I31,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B32" s="12">
         <v>46188</v>
       </c>
@@ -4509,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="9" t="str">
-        <f t="shared" ref="M32:M36" si="20">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(J32-L32)=SIGN($G32-$I32),1,0)+IF(J32=$G32,IF(L32=$I32,2,0),0))</f>
+        <f t="shared" ref="M32:M36" si="24">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(J32-L32)=SIGN($G32-$I32),1,0)+IF(J32=$G32,IF(L32=$I32,2,0),0))</f>
         <v/>
       </c>
       <c r="N32" s="3">
@@ -4522,7 +4911,7 @@
         <v>2</v>
       </c>
       <c r="Q32" s="9" t="str">
-        <f t="shared" ref="Q32:Q36" si="21">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(N32-P32)=SIGN($G32-$I32),1,0)+IF(N32=$G32,IF(P32=$I32,2,0),0))</f>
+        <f t="shared" ref="Q32:Q36" si="25">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(N32-P32)=SIGN($G32-$I32),1,0)+IF(N32=$G32,IF(P32=$I32,2,0),0))</f>
         <v/>
       </c>
       <c r="R32" s="3">
@@ -4535,7 +4924,7 @@
         <v>1</v>
       </c>
       <c r="U32" s="9" t="str">
-        <f t="shared" ref="U32:U36" si="22">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(R32-T32)=SIGN($G32-$I32),1,0)+IF(R32=$G32,IF(T32=$I32,2,0),0))</f>
+        <f t="shared" ref="U32:U36" si="26">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(R32-T32)=SIGN($G32-$I32),1,0)+IF(R32=$G32,IF(T32=$I32,2,0),0))</f>
         <v/>
       </c>
       <c r="V32" s="3"/>
@@ -4544,7 +4933,7 @@
       </c>
       <c r="X32" s="7"/>
       <c r="Y32" s="9" t="str">
-        <f t="shared" ref="Y32:Y36" si="23">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(V32-X32)=SIGN($G32-$I32),1,0)+IF(V32=$G32,IF(X32=$I32,2,0),0))</f>
+        <f t="shared" ref="Y32:Y36" si="27">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(V32-X32)=SIGN($G32-$I32),1,0)+IF(V32=$G32,IF(X32=$I32,2,0),0))</f>
         <v/>
       </c>
       <c r="Z32" s="3">
@@ -4557,11 +4946,24 @@
         <v>2</v>
       </c>
       <c r="AC32" s="9" t="str">
-        <f t="shared" ref="AC32:AC36" si="24">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(Z32-AB32)=SIGN($G32-$I32),1,0)+IF(Z32=$G32,IF(AB32=$I32,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC32:AC36" si="28">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(Z32-AB32)=SIGN($G32-$I32),1,0)+IF(Z32=$G32,IF(AB32=$I32,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD32" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="9" t="str">
+        <f t="shared" ref="AG32:AG36" si="29">IF(ISBLANK($G32)=TRUE,"",IF(SIGN(AD32-AF32)=SIGN($G32-$I32),1,0)+IF(AD32=$G32,IF(AF32=$I32,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B33" s="12">
         <v>46193</v>
       </c>
@@ -4592,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N33" s="3">
@@ -4605,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="Q33" s="9" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="R33" s="3">
@@ -4618,7 +5020,7 @@
         <v>1</v>
       </c>
       <c r="U33" s="9" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="V33" s="3"/>
@@ -4627,7 +5029,7 @@
       </c>
       <c r="X33" s="7"/>
       <c r="Y33" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Z33" s="3">
@@ -4640,11 +5042,24 @@
         <v>0</v>
       </c>
       <c r="AC33" s="9" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="AD33" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="9" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B34" s="12">
         <v>46194</v>
       </c>
@@ -4675,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N34" s="3">
@@ -4688,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="9" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="R34" s="3">
@@ -4701,7 +5116,7 @@
         <v>0</v>
       </c>
       <c r="U34" s="9" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="V34" s="3"/>
@@ -4710,7 +5125,7 @@
       </c>
       <c r="X34" s="7"/>
       <c r="Y34" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Z34" s="3">
@@ -4723,11 +5138,24 @@
         <v>2</v>
       </c>
       <c r="AC34" s="9" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="AD34" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="9" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B35" s="12">
         <v>46198</v>
       </c>
@@ -4758,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="M35" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N35" s="3">
@@ -4771,7 +5199,7 @@
         <v>3</v>
       </c>
       <c r="Q35" s="9" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="R35" s="3">
@@ -4784,7 +5212,7 @@
         <v>6</v>
       </c>
       <c r="U35" s="9" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="V35" s="3"/>
@@ -4793,7 +5221,7 @@
       </c>
       <c r="X35" s="7"/>
       <c r="Y35" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Z35" s="3">
@@ -4806,11 +5234,24 @@
         <v>4</v>
       </c>
       <c r="AC35" s="9" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="7">
+        <v>4</v>
+      </c>
+      <c r="AG35" s="9" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="13">
         <v>46198</v>
       </c>
@@ -4841,7 +5282,7 @@
         <v>2</v>
       </c>
       <c r="M36" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N36" s="4">
@@ -4854,7 +5295,7 @@
         <v>2</v>
       </c>
       <c r="Q36" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="R36" s="4">
@@ -4867,7 +5308,7 @@
         <v>1</v>
       </c>
       <c r="U36" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="V36" s="4"/>
@@ -4876,7 +5317,7 @@
       </c>
       <c r="X36" s="8"/>
       <c r="Y36" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Z36" s="4">
@@ -4889,22 +5330,35 @@
         <v>3</v>
       </c>
       <c r="AC36" s="10" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="AD36" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="8">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="10" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D37" s="83" t="s">
+      <c r="D37" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="E37" s="84"/>
-      <c r="F37" s="85"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="104"/>
       <c r="G37" s="72" t="s">
         <v>7</v>
       </c>
@@ -4930,8 +5384,12 @@
       <c r="AA37" s="51"/>
       <c r="AB37" s="51"/>
       <c r="AC37" s="52"/>
-    </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD37" s="83"/>
+      <c r="AE37" s="84"/>
+      <c r="AF37" s="84"/>
+      <c r="AG37" s="85"/>
+    </row>
+    <row r="38" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B38" s="12">
         <v>46187</v>
       </c>
@@ -5013,8 +5471,21 @@
         <f>IF(ISBLANK($I38)=TRUE,"",IF(SIGN(Z38-AB38)=SIGN($G38-$I38),1,0)+IF(Z38=$G38,IF(AB38=$I38,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD38" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="11" t="str">
+        <f>IF(ISBLANK($I38)=TRUE,"",IF(SIGN(AD38-AF38)=SIGN($G38-$I38),1,0)+IF(AD38=$G38,IF(AF38=$I38,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B39" s="12">
         <v>46188</v>
       </c>
@@ -5045,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="9" t="str">
-        <f t="shared" ref="M39:M43" si="25">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(J39-L39)=SIGN($G39-$I39),1,0)+IF(J39=$G39,IF(L39=$I39,2,0),0))</f>
+        <f t="shared" ref="M39:M43" si="30">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(J39-L39)=SIGN($G39-$I39),1,0)+IF(J39=$G39,IF(L39=$I39,2,0),0))</f>
         <v/>
       </c>
       <c r="N39" s="3">
@@ -5058,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="Q39" s="9" t="str">
-        <f t="shared" ref="Q39:Q43" si="26">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(N39-P39)=SIGN($G39-$I39),1,0)+IF(N39=$G39,IF(P39=$I39,2,0),0))</f>
+        <f t="shared" ref="Q39:Q43" si="31">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(N39-P39)=SIGN($G39-$I39),1,0)+IF(N39=$G39,IF(P39=$I39,2,0),0))</f>
         <v/>
       </c>
       <c r="R39" s="3">
@@ -5071,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="9" t="str">
-        <f t="shared" ref="U39:U43" si="27">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(R39-T39)=SIGN($G39-$I39),1,0)+IF(R39=$G39,IF(T39=$I39,2,0),0))</f>
+        <f t="shared" ref="U39:U43" si="32">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(R39-T39)=SIGN($G39-$I39),1,0)+IF(R39=$G39,IF(T39=$I39,2,0),0))</f>
         <v/>
       </c>
       <c r="V39" s="3"/>
@@ -5080,7 +5551,7 @@
       </c>
       <c r="X39" s="7"/>
       <c r="Y39" s="9" t="str">
-        <f t="shared" ref="Y39:Y43" si="28">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(V39-X39)=SIGN($G39-$I39),1,0)+IF(V39=$G39,IF(X39=$I39,2,0),0))</f>
+        <f t="shared" ref="Y39:Y43" si="33">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(V39-X39)=SIGN($G39-$I39),1,0)+IF(V39=$G39,IF(X39=$I39,2,0),0))</f>
         <v/>
       </c>
       <c r="Z39" s="3">
@@ -5093,11 +5564,24 @@
         <v>2</v>
       </c>
       <c r="AC39" s="9" t="str">
-        <f t="shared" ref="AC39:AC43" si="29">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(Z39-AB39)=SIGN($G39-$I39),1,0)+IF(Z39=$G39,IF(AB39=$I39,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC39:AC43" si="34">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(Z39-AB39)=SIGN($G39-$I39),1,0)+IF(Z39=$G39,IF(AB39=$I39,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD39" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG39" s="9" t="str">
+        <f t="shared" ref="AG39:AG43" si="35">IF(ISBLANK($G39)=TRUE,"",IF(SIGN(AD39-AF39)=SIGN($G39-$I39),1,0)+IF(AD39=$G39,IF(AF39=$I39,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B40" s="12">
         <v>46193</v>
       </c>
@@ -5128,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="9" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="N40" s="3">
@@ -5141,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="Q40" s="9" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="R40" s="3">
@@ -5154,7 +5638,7 @@
         <v>1</v>
       </c>
       <c r="U40" s="9" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="V40" s="3"/>
@@ -5163,7 +5647,7 @@
       </c>
       <c r="X40" s="7"/>
       <c r="Y40" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Z40" s="3">
@@ -5176,11 +5660,24 @@
         <v>1</v>
       </c>
       <c r="AC40" s="9" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AD40" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF40" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="9" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B41" s="12">
         <v>46194</v>
       </c>
@@ -5211,7 +5708,7 @@
         <v>2</v>
       </c>
       <c r="M41" s="9" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="N41" s="3">
@@ -5224,7 +5721,7 @@
         <v>2</v>
       </c>
       <c r="Q41" s="9" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="R41" s="3">
@@ -5237,7 +5734,7 @@
         <v>2</v>
       </c>
       <c r="U41" s="9" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="V41" s="3"/>
@@ -5246,7 +5743,7 @@
       </c>
       <c r="X41" s="7"/>
       <c r="Y41" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Z41" s="3">
@@ -5259,11 +5756,24 @@
         <v>0</v>
       </c>
       <c r="AC41" s="9" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AD41" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG41" s="9" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B42" s="12">
         <v>46199</v>
       </c>
@@ -5294,7 +5804,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="9" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="N42" s="3">
@@ -5307,7 +5817,7 @@
         <v>2</v>
       </c>
       <c r="Q42" s="9" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="R42" s="3">
@@ -5320,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="U42" s="9" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="V42" s="3"/>
@@ -5329,7 +5839,7 @@
       </c>
       <c r="X42" s="7"/>
       <c r="Y42" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Z42" s="3">
@@ -5342,11 +5852,24 @@
         <v>0</v>
       </c>
       <c r="AC42" s="9" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AD42" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="9" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="13">
         <v>46199</v>
       </c>
@@ -5377,7 +5900,7 @@
         <v>2</v>
       </c>
       <c r="M43" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="N43" s="4">
@@ -5390,7 +5913,7 @@
         <v>3</v>
       </c>
       <c r="Q43" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="R43" s="4">
@@ -5403,7 +5926,7 @@
         <v>3</v>
       </c>
       <c r="U43" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="V43" s="4"/>
@@ -5412,7 +5935,7 @@
       </c>
       <c r="X43" s="8"/>
       <c r="Y43" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Z43" s="4">
@@ -5425,22 +5948,35 @@
         <v>2</v>
       </c>
       <c r="AC43" s="10" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AD43" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE43" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF43" s="8">
+        <v>1</v>
+      </c>
+      <c r="AG43" s="10" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C44" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D44" s="83" t="s">
+      <c r="D44" s="102" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="84"/>
-      <c r="F44" s="85"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="104"/>
       <c r="G44" s="72" t="s">
         <v>7</v>
       </c>
@@ -5466,8 +6002,12 @@
       <c r="AA44" s="51"/>
       <c r="AB44" s="51"/>
       <c r="AC44" s="52"/>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD44" s="83"/>
+      <c r="AE44" s="84"/>
+      <c r="AF44" s="84"/>
+      <c r="AG44" s="85"/>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B45" s="12">
         <v>46188</v>
       </c>
@@ -5549,8 +6089,21 @@
         <f>IF(ISBLANK($I45)=TRUE,"",IF(SIGN(Z45-AB45)=SIGN($G45-$I45),1,0)+IF(Z45=$G45,IF(AB45=$I45,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD45" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF45" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG45" s="11" t="str">
+        <f>IF(ISBLANK($I45)=TRUE,"",IF(SIGN(AD45-AF45)=SIGN($G45-$I45),1,0)+IF(AD45=$G45,IF(AF45=$I45,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B46" s="12">
         <v>46189</v>
       </c>
@@ -5581,7 +6134,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="9" t="str">
-        <f t="shared" ref="M46:M50" si="30">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(J46-L46)=SIGN($G46-$I46),1,0)+IF(J46=$G46,IF(L46=$I46,2,0),0))</f>
+        <f t="shared" ref="M46:M50" si="36">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(J46-L46)=SIGN($G46-$I46),1,0)+IF(J46=$G46,IF(L46=$I46,2,0),0))</f>
         <v/>
       </c>
       <c r="N46" s="3">
@@ -5594,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="Q46" s="9" t="str">
-        <f t="shared" ref="Q46:Q50" si="31">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(N46-P46)=SIGN($G46-$I46),1,0)+IF(N46=$G46,IF(P46=$I46,2,0),0))</f>
+        <f t="shared" ref="Q46:Q50" si="37">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(N46-P46)=SIGN($G46-$I46),1,0)+IF(N46=$G46,IF(P46=$I46,2,0),0))</f>
         <v/>
       </c>
       <c r="R46" s="3">
@@ -5607,7 +6160,7 @@
         <v>1</v>
       </c>
       <c r="U46" s="9" t="str">
-        <f t="shared" ref="U46:U50" si="32">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(R46-T46)=SIGN($G46-$I46),1,0)+IF(R46=$G46,IF(T46=$I46,2,0),0))</f>
+        <f t="shared" ref="U46:U50" si="38">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(R46-T46)=SIGN($G46-$I46),1,0)+IF(R46=$G46,IF(T46=$I46,2,0),0))</f>
         <v/>
       </c>
       <c r="V46" s="3"/>
@@ -5616,7 +6169,7 @@
       </c>
       <c r="X46" s="7"/>
       <c r="Y46" s="9" t="str">
-        <f t="shared" ref="Y46:Y50" si="33">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(V46-X46)=SIGN($G46-$I46),1,0)+IF(V46=$G46,IF(X46=$I46,2,0),0))</f>
+        <f t="shared" ref="Y46:Y50" si="39">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(V46-X46)=SIGN($G46-$I46),1,0)+IF(V46=$G46,IF(X46=$I46,2,0),0))</f>
         <v/>
       </c>
       <c r="Z46" s="3">
@@ -5629,11 +6182,24 @@
         <v>3</v>
       </c>
       <c r="AC46" s="9" t="str">
-        <f t="shared" ref="AC46:AC50" si="34">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(Z46-AB46)=SIGN($G46-$I46),1,0)+IF(Z46=$G46,IF(AB46=$I46,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC46:AC50" si="40">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(Z46-AB46)=SIGN($G46-$I46),1,0)+IF(Z46=$G46,IF(AB46=$I46,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD46" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF46" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="9" t="str">
+        <f t="shared" ref="AG46:AG50" si="41">IF(ISBLANK($G46)=TRUE,"",IF(SIGN(AD46-AF46)=SIGN($G46-$I46),1,0)+IF(AD46=$G46,IF(AF46=$I46,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B47" s="12">
         <v>46194</v>
       </c>
@@ -5664,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="9" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="N47" s="3">
@@ -5677,7 +6243,7 @@
         <v>1</v>
       </c>
       <c r="Q47" s="9" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R47" s="3">
@@ -5690,7 +6256,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="V47" s="3"/>
@@ -5699,7 +6265,7 @@
       </c>
       <c r="X47" s="7"/>
       <c r="Y47" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Z47" s="3">
@@ -5712,11 +6278,24 @@
         <v>0</v>
       </c>
       <c r="AC47" s="9" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AD47" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF47" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="9" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B48" s="12">
         <v>46195</v>
       </c>
@@ -5747,7 +6326,7 @@
         <v>2</v>
       </c>
       <c r="M48" s="9" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="N48" s="3">
@@ -5760,7 +6339,7 @@
         <v>2</v>
       </c>
       <c r="Q48" s="9" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R48" s="3">
@@ -5773,7 +6352,7 @@
         <v>2</v>
       </c>
       <c r="U48" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="V48" s="3"/>
@@ -5782,7 +6361,7 @@
       </c>
       <c r="X48" s="7"/>
       <c r="Y48" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Z48" s="3">
@@ -5795,11 +6374,24 @@
         <v>0</v>
       </c>
       <c r="AC48" s="9" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF48" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG48" s="9" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B49" s="12">
         <v>46200</v>
       </c>
@@ -5830,7 +6422,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="9" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="N49" s="3">
@@ -5843,7 +6435,7 @@
         <v>1</v>
       </c>
       <c r="Q49" s="9" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R49" s="3">
@@ -5856,7 +6448,7 @@
         <v>1</v>
       </c>
       <c r="U49" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="V49" s="3"/>
@@ -5865,7 +6457,7 @@
       </c>
       <c r="X49" s="7"/>
       <c r="Y49" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Z49" s="3">
@@ -5878,11 +6470,24 @@
         <v>0</v>
       </c>
       <c r="AC49" s="9" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AD49" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF49" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG49" s="9" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="13">
         <v>46200</v>
       </c>
@@ -5913,7 +6518,7 @@
         <v>2</v>
       </c>
       <c r="M50" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="N50" s="4">
@@ -5926,7 +6531,7 @@
         <v>2</v>
       </c>
       <c r="Q50" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R50" s="4">
@@ -5939,7 +6544,7 @@
         <v>2</v>
       </c>
       <c r="U50" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="V50" s="4"/>
@@ -5948,7 +6553,7 @@
       </c>
       <c r="X50" s="8"/>
       <c r="Y50" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Z50" s="4">
@@ -5961,22 +6566,35 @@
         <v>2</v>
       </c>
       <c r="AC50" s="10" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AD50" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF50" s="8">
+        <v>2</v>
+      </c>
+      <c r="AG50" s="10" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C51" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D51" s="83" t="s">
+      <c r="D51" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="E51" s="84"/>
-      <c r="F51" s="85"/>
+      <c r="E51" s="103"/>
+      <c r="F51" s="104"/>
       <c r="G51" s="72" t="s">
         <v>7</v>
       </c>
@@ -6002,8 +6620,12 @@
       <c r="AA51" s="51"/>
       <c r="AB51" s="51"/>
       <c r="AC51" s="52"/>
-    </row>
-    <row r="52" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD51" s="83"/>
+      <c r="AE51" s="84"/>
+      <c r="AF51" s="84"/>
+      <c r="AG51" s="85"/>
+    </row>
+    <row r="52" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B52" s="12">
         <v>46188</v>
       </c>
@@ -6085,8 +6707,21 @@
         <f>IF(ISBLANK($I52)=TRUE,"",IF(SIGN(Z52-AB52)=SIGN($G52-$I52),1,0)+IF(Z52=$G52,IF(AB52=$I52,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="53" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD52" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF52" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="11" t="str">
+        <f>IF(ISBLANK($I52)=TRUE,"",IF(SIGN(AD52-AF52)=SIGN($G52-$I52),1,0)+IF(AD52=$G52,IF(AF52=$I52,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B53" s="12">
         <v>46189</v>
       </c>
@@ -6117,7 +6752,7 @@
         <v>2</v>
       </c>
       <c r="M53" s="9" t="str">
-        <f t="shared" ref="M53:M57" si="35">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(J53-L53)=SIGN($G53-$I53),1,0)+IF(J53=$G53,IF(L53=$I53,2,0),0))</f>
+        <f t="shared" ref="M53:M57" si="42">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(J53-L53)=SIGN($G53-$I53),1,0)+IF(J53=$G53,IF(L53=$I53,2,0),0))</f>
         <v/>
       </c>
       <c r="N53" s="3">
@@ -6130,7 +6765,7 @@
         <v>2</v>
       </c>
       <c r="Q53" s="9" t="str">
-        <f t="shared" ref="Q53:Q57" si="36">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(N53-P53)=SIGN($G53-$I53),1,0)+IF(N53=$G53,IF(P53=$I53,2,0),0))</f>
+        <f t="shared" ref="Q53:Q57" si="43">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(N53-P53)=SIGN($G53-$I53),1,0)+IF(N53=$G53,IF(P53=$I53,2,0),0))</f>
         <v/>
       </c>
       <c r="R53" s="3">
@@ -6143,7 +6778,7 @@
         <v>2</v>
       </c>
       <c r="U53" s="9" t="str">
-        <f t="shared" ref="U53:U57" si="37">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(R53-T53)=SIGN($G53-$I53),1,0)+IF(R53=$G53,IF(T53=$I53,2,0),0))</f>
+        <f t="shared" ref="U53:U57" si="44">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(R53-T53)=SIGN($G53-$I53),1,0)+IF(R53=$G53,IF(T53=$I53,2,0),0))</f>
         <v/>
       </c>
       <c r="V53" s="3"/>
@@ -6152,7 +6787,7 @@
       </c>
       <c r="X53" s="7"/>
       <c r="Y53" s="9" t="str">
-        <f t="shared" ref="Y53:Y57" si="38">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(V53-X53)=SIGN($G53-$I53),1,0)+IF(V53=$G53,IF(X53=$I53,2,0),0))</f>
+        <f t="shared" ref="Y53:Y57" si="45">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(V53-X53)=SIGN($G53-$I53),1,0)+IF(V53=$G53,IF(X53=$I53,2,0),0))</f>
         <v/>
       </c>
       <c r="Z53" s="3">
@@ -6165,11 +6800,24 @@
         <v>1</v>
       </c>
       <c r="AC53" s="9" t="str">
-        <f t="shared" ref="AC53:AC57" si="39">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(Z53-AB53)=SIGN($G53-$I53),1,0)+IF(Z53=$G53,IF(AB53=$I53,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC53:AC57" si="46">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(Z53-AB53)=SIGN($G53-$I53),1,0)+IF(Z53=$G53,IF(AB53=$I53,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF53" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG53" s="9" t="str">
+        <f t="shared" ref="AG53:AG57" si="47">IF(ISBLANK($G53)=TRUE,"",IF(SIGN(AD53-AF53)=SIGN($G53-$I53),1,0)+IF(AD53=$G53,IF(AF53=$I53,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B54" s="12">
         <v>46194</v>
       </c>
@@ -6200,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="9" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="N54" s="3">
@@ -6213,7 +6861,7 @@
         <v>1</v>
       </c>
       <c r="Q54" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="R54" s="3">
@@ -6226,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="V54" s="3"/>
@@ -6235,7 +6883,7 @@
       </c>
       <c r="X54" s="7"/>
       <c r="Y54" s="9" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Z54" s="3">
@@ -6248,11 +6896,24 @@
         <v>0</v>
       </c>
       <c r="AC54" s="9" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AD54" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF54" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="9" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B55" s="12">
         <v>46195</v>
       </c>
@@ -6283,7 +6944,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="9" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="N55" s="3">
@@ -6296,7 +6957,7 @@
         <v>0</v>
       </c>
       <c r="Q55" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="R55" s="3">
@@ -6309,7 +6970,7 @@
         <v>1</v>
       </c>
       <c r="U55" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="V55" s="3"/>
@@ -6318,7 +6979,7 @@
       </c>
       <c r="X55" s="7"/>
       <c r="Y55" s="9" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Z55" s="3">
@@ -6331,11 +6992,24 @@
         <v>1</v>
       </c>
       <c r="AC55" s="9" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AD55" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="9" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B56" s="12">
         <v>46200</v>
       </c>
@@ -6366,7 +7040,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="9" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="N56" s="3">
@@ -6379,7 +7053,7 @@
         <v>2</v>
       </c>
       <c r="Q56" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="R56" s="3">
@@ -6392,7 +7066,7 @@
         <v>2</v>
       </c>
       <c r="U56" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="V56" s="3"/>
@@ -6401,7 +7075,7 @@
       </c>
       <c r="X56" s="7"/>
       <c r="Y56" s="9" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Z56" s="3">
@@ -6414,11 +7088,24 @@
         <v>3</v>
       </c>
       <c r="AC56" s="9" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AD56" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG56" s="9" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="13">
         <v>46200</v>
       </c>
@@ -6449,7 +7136,7 @@
         <v>2</v>
       </c>
       <c r="M57" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="N57" s="4">
@@ -6462,7 +7149,7 @@
         <v>2</v>
       </c>
       <c r="Q57" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="R57" s="4">
@@ -6475,7 +7162,7 @@
         <v>3</v>
       </c>
       <c r="U57" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="V57" s="4"/>
@@ -6484,7 +7171,7 @@
       </c>
       <c r="X57" s="8"/>
       <c r="Y57" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Z57" s="4">
@@ -6497,22 +7184,35 @@
         <v>2</v>
       </c>
       <c r="AC57" s="10" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AD57" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE57" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF57" s="8">
+        <v>1</v>
+      </c>
+      <c r="AG57" s="10" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C58" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D58" s="83" t="s">
+      <c r="D58" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="E58" s="84"/>
-      <c r="F58" s="85"/>
+      <c r="E58" s="103"/>
+      <c r="F58" s="104"/>
       <c r="G58" s="72" t="s">
         <v>7</v>
       </c>
@@ -6538,8 +7238,12 @@
       <c r="AA58" s="51"/>
       <c r="AB58" s="51"/>
       <c r="AC58" s="52"/>
-    </row>
-    <row r="59" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD58" s="83"/>
+      <c r="AE58" s="84"/>
+      <c r="AF58" s="84"/>
+      <c r="AG58" s="85"/>
+    </row>
+    <row r="59" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B59" s="12">
         <v>46189</v>
       </c>
@@ -6621,8 +7325,21 @@
         <f>IF(ISBLANK($I59)=TRUE,"",IF(SIGN(Z59-AB59)=SIGN($G59-$I59),1,0)+IF(Z59=$G59,IF(AB59=$I59,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="60" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD59" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF59" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG59" s="11" t="str">
+        <f>IF(ISBLANK($I59)=TRUE,"",IF(SIGN(AD59-AF59)=SIGN($G59-$I59),1,0)+IF(AD59=$G59,IF(AF59=$I59,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B60" s="12">
         <v>46190</v>
       </c>
@@ -6653,7 +7370,7 @@
         <v>2</v>
       </c>
       <c r="M60" s="9" t="str">
-        <f t="shared" ref="M60:M64" si="40">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(J60-L60)=SIGN($G60-$I60),1,0)+IF(J60=$G60,IF(L60=$I60,2,0),0))</f>
+        <f t="shared" ref="M60:M64" si="48">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(J60-L60)=SIGN($G60-$I60),1,0)+IF(J60=$G60,IF(L60=$I60,2,0),0))</f>
         <v/>
       </c>
       <c r="N60" s="3">
@@ -6666,7 +7383,7 @@
         <v>2</v>
       </c>
       <c r="Q60" s="9" t="str">
-        <f t="shared" ref="Q60:Q64" si="41">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(N60-P60)=SIGN($G60-$I60),1,0)+IF(N60=$G60,IF(P60=$I60,2,0),0))</f>
+        <f t="shared" ref="Q60:Q64" si="49">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(N60-P60)=SIGN($G60-$I60),1,0)+IF(N60=$G60,IF(P60=$I60,2,0),0))</f>
         <v/>
       </c>
       <c r="R60" s="3">
@@ -6679,7 +7396,7 @@
         <v>2</v>
       </c>
       <c r="U60" s="9" t="str">
-        <f t="shared" ref="U60:U64" si="42">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(R60-T60)=SIGN($G60-$I60),1,0)+IF(R60=$G60,IF(T60=$I60,2,0),0))</f>
+        <f t="shared" ref="U60:U64" si="50">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(R60-T60)=SIGN($G60-$I60),1,0)+IF(R60=$G60,IF(T60=$I60,2,0),0))</f>
         <v/>
       </c>
       <c r="V60" s="3"/>
@@ -6688,7 +7405,7 @@
       </c>
       <c r="X60" s="7"/>
       <c r="Y60" s="9" t="str">
-        <f t="shared" ref="Y60:Y64" si="43">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(V60-X60)=SIGN($G60-$I60),1,0)+IF(V60=$G60,IF(X60=$I60,2,0),0))</f>
+        <f t="shared" ref="Y60:Y64" si="51">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(V60-X60)=SIGN($G60-$I60),1,0)+IF(V60=$G60,IF(X60=$I60,2,0),0))</f>
         <v/>
       </c>
       <c r="Z60" s="3">
@@ -6701,11 +7418,24 @@
         <v>4</v>
       </c>
       <c r="AC60" s="9" t="str">
-        <f t="shared" ref="AC60:AC64" si="44">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(Z60-AB60)=SIGN($G60-$I60),1,0)+IF(Z60=$G60,IF(AB60=$I60,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC60:AC64" si="52">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(Z60-AB60)=SIGN($G60-$I60),1,0)+IF(Z60=$G60,IF(AB60=$I60,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF60" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG60" s="9" t="str">
+        <f t="shared" ref="AG60:AG64" si="53">IF(ISBLANK($G60)=TRUE,"",IF(SIGN(AD60-AF60)=SIGN($G60-$I60),1,0)+IF(AD60=$G60,IF(AF60=$I60,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B61" s="12">
         <v>46195</v>
       </c>
@@ -6736,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="9" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="N61" s="3">
@@ -6749,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="9" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="R61" s="3">
@@ -6762,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="9" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="V61" s="3"/>
@@ -6771,7 +7501,7 @@
       </c>
       <c r="X61" s="7"/>
       <c r="Y61" s="9" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="Z61" s="3">
@@ -6784,11 +7514,24 @@
         <v>1</v>
       </c>
       <c r="AC61" s="9" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="52"/>
+        <v/>
+      </c>
+      <c r="AD61" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF61" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="9" t="str">
+        <f t="shared" si="53"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B62" s="12">
         <v>46196</v>
       </c>
@@ -6819,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="9" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="N62" s="3">
@@ -6832,7 +7575,7 @@
         <v>1</v>
       </c>
       <c r="Q62" s="9" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="R62" s="3">
@@ -6845,7 +7588,7 @@
         <v>2</v>
       </c>
       <c r="U62" s="9" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="V62" s="3"/>
@@ -6854,7 +7597,7 @@
       </c>
       <c r="X62" s="7"/>
       <c r="Y62" s="9" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="Z62" s="3">
@@ -6867,11 +7610,24 @@
         <v>0</v>
       </c>
       <c r="AC62" s="9" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="52"/>
+        <v/>
+      </c>
+      <c r="AD62" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF62" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG62" s="9" t="str">
+        <f t="shared" si="53"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B63" s="12">
         <v>46199</v>
       </c>
@@ -6902,7 +7658,7 @@
         <v>2</v>
       </c>
       <c r="M63" s="9" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="N63" s="3">
@@ -6915,7 +7671,7 @@
         <v>2</v>
       </c>
       <c r="Q63" s="9" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="R63" s="3">
@@ -6928,7 +7684,7 @@
         <v>2</v>
       </c>
       <c r="U63" s="9" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="V63" s="3"/>
@@ -6937,7 +7693,7 @@
       </c>
       <c r="X63" s="7"/>
       <c r="Y63" s="9" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="Z63" s="3">
@@ -6950,11 +7706,24 @@
         <v>2</v>
       </c>
       <c r="AC63" s="9" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="52"/>
+        <v/>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF63" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG63" s="9" t="str">
+        <f t="shared" si="53"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="13">
         <v>46199</v>
       </c>
@@ -6985,7 +7754,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="N64" s="4">
@@ -6998,7 +7767,7 @@
         <v>1</v>
       </c>
       <c r="Q64" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="R64" s="4">
@@ -7011,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="V64" s="4"/>
@@ -7020,7 +7789,7 @@
       </c>
       <c r="X64" s="8"/>
       <c r="Y64" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="Z64" s="4">
@@ -7033,22 +7802,35 @@
         <v>0</v>
       </c>
       <c r="AC64" s="10" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="52"/>
+        <v/>
+      </c>
+      <c r="AD64" s="4">
+        <v>2</v>
+      </c>
+      <c r="AE64" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF64" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="10" t="str">
+        <f t="shared" si="53"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C65" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D65" s="83" t="s">
+      <c r="D65" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="E65" s="84"/>
-      <c r="F65" s="85"/>
+      <c r="E65" s="103"/>
+      <c r="F65" s="104"/>
       <c r="G65" s="72" t="s">
         <v>7</v>
       </c>
@@ -7074,8 +7856,12 @@
       <c r="AA65" s="51"/>
       <c r="AB65" s="51"/>
       <c r="AC65" s="52"/>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD65" s="83"/>
+      <c r="AE65" s="84"/>
+      <c r="AF65" s="84"/>
+      <c r="AG65" s="85"/>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B66" s="12">
         <v>46190</v>
       </c>
@@ -7157,8 +7943,21 @@
         <f>IF(ISBLANK($I66)=TRUE,"",IF(SIGN(Z66-AB66)=SIGN($G66-$I66),1,0)+IF(Z66=$G66,IF(AB66=$I66,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD66" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF66" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG66" s="11" t="str">
+        <f>IF(ISBLANK($I66)=TRUE,"",IF(SIGN(AD66-AF66)=SIGN($G66-$I66),1,0)+IF(AD66=$G66,IF(AF66=$I66,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B67" s="12">
         <v>46190</v>
       </c>
@@ -7189,7 +7988,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="9" t="str">
-        <f t="shared" ref="M67:M71" si="45">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(J67-L67)=SIGN($G67-$I67),1,0)+IF(J67=$G67,IF(L67=$I67,2,0),0))</f>
+        <f t="shared" ref="M67:M71" si="54">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(J67-L67)=SIGN($G67-$I67),1,0)+IF(J67=$G67,IF(L67=$I67,2,0),0))</f>
         <v/>
       </c>
       <c r="N67" s="3">
@@ -7202,7 +8001,7 @@
         <v>1</v>
       </c>
       <c r="Q67" s="9" t="str">
-        <f t="shared" ref="Q67:Q71" si="46">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(N67-P67)=SIGN($G67-$I67),1,0)+IF(N67=$G67,IF(P67=$I67,2,0),0))</f>
+        <f t="shared" ref="Q67:Q71" si="55">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(N67-P67)=SIGN($G67-$I67),1,0)+IF(N67=$G67,IF(P67=$I67,2,0),0))</f>
         <v/>
       </c>
       <c r="R67" s="3">
@@ -7215,7 +8014,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="9" t="str">
-        <f t="shared" ref="U67:U71" si="47">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(R67-T67)=SIGN($G67-$I67),1,0)+IF(R67=$G67,IF(T67=$I67,2,0),0))</f>
+        <f t="shared" ref="U67:U71" si="56">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(R67-T67)=SIGN($G67-$I67),1,0)+IF(R67=$G67,IF(T67=$I67,2,0),0))</f>
         <v/>
       </c>
       <c r="V67" s="3"/>
@@ -7224,7 +8023,7 @@
       </c>
       <c r="X67" s="7"/>
       <c r="Y67" s="9" t="str">
-        <f t="shared" ref="Y67:Y71" si="48">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(V67-X67)=SIGN($G67-$I67),1,0)+IF(V67=$G67,IF(X67=$I67,2,0),0))</f>
+        <f t="shared" ref="Y67:Y71" si="57">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(V67-X67)=SIGN($G67-$I67),1,0)+IF(V67=$G67,IF(X67=$I67,2,0),0))</f>
         <v/>
       </c>
       <c r="Z67" s="3">
@@ -7237,11 +8036,24 @@
         <v>0</v>
       </c>
       <c r="AC67" s="9" t="str">
-        <f t="shared" ref="AC67:AC71" si="49">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(Z67-AB67)=SIGN($G67-$I67),1,0)+IF(Z67=$G67,IF(AB67=$I67,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC67:AC71" si="58">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(Z67-AB67)=SIGN($G67-$I67),1,0)+IF(Z67=$G67,IF(AB67=$I67,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD67" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF67" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG67" s="9" t="str">
+        <f t="shared" ref="AG67:AG71" si="59">IF(ISBLANK($G67)=TRUE,"",IF(SIGN(AD67-AF67)=SIGN($G67-$I67),1,0)+IF(AD67=$G67,IF(AF67=$I67,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B68" s="12">
         <v>46195</v>
       </c>
@@ -7272,7 +8084,7 @@
         <v>1</v>
       </c>
       <c r="M68" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="N68" s="3">
@@ -7285,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="9" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="R68" s="3">
@@ -7298,7 +8110,7 @@
         <v>1</v>
       </c>
       <c r="U68" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="V68" s="3"/>
@@ -7307,7 +8119,7 @@
       </c>
       <c r="X68" s="7"/>
       <c r="Y68" s="9" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="Z68" s="3">
@@ -7320,11 +8132,24 @@
         <v>0</v>
       </c>
       <c r="AC68" s="9" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="58"/>
+        <v/>
+      </c>
+      <c r="AD68" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF68" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="9" t="str">
+        <f t="shared" si="59"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B69" s="12">
         <v>46196</v>
       </c>
@@ -7355,7 +8180,7 @@
         <v>2</v>
       </c>
       <c r="M69" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="N69" s="3">
@@ -7368,7 +8193,7 @@
         <v>1</v>
       </c>
       <c r="Q69" s="9" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="R69" s="3">
@@ -7381,7 +8206,7 @@
         <v>2</v>
       </c>
       <c r="U69" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="V69" s="3"/>
@@ -7390,7 +8215,7 @@
       </c>
       <c r="X69" s="7"/>
       <c r="Y69" s="9" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="Z69" s="3">
@@ -7403,11 +8228,24 @@
         <v>0</v>
       </c>
       <c r="AC69" s="9" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="58"/>
+        <v/>
+      </c>
+      <c r="AD69" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF69" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG69" s="9" t="str">
+        <f t="shared" si="59"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B70" s="12">
         <v>46201</v>
       </c>
@@ -7438,7 +8276,7 @@
         <v>1</v>
       </c>
       <c r="M70" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="N70" s="3">
@@ -7451,7 +8289,7 @@
         <v>2</v>
       </c>
       <c r="Q70" s="9" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="R70" s="3">
@@ -7464,7 +8302,7 @@
         <v>1</v>
       </c>
       <c r="U70" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="V70" s="3"/>
@@ -7473,7 +8311,7 @@
       </c>
       <c r="X70" s="7"/>
       <c r="Y70" s="9" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="Z70" s="3">
@@ -7486,11 +8324,24 @@
         <v>1</v>
       </c>
       <c r="AC70" s="9" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="58"/>
+        <v/>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF70" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG70" s="9" t="str">
+        <f t="shared" si="59"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="13">
         <v>46201</v>
       </c>
@@ -7521,7 +8372,7 @@
         <v>3</v>
       </c>
       <c r="M71" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="N71" s="4">
@@ -7534,7 +8385,7 @@
         <v>3</v>
       </c>
       <c r="Q71" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="R71" s="4">
@@ -7547,7 +8398,7 @@
         <v>4</v>
       </c>
       <c r="U71" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="V71" s="4"/>
@@ -7556,7 +8407,7 @@
       </c>
       <c r="X71" s="8"/>
       <c r="Y71" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="Z71" s="4">
@@ -7569,22 +8420,35 @@
         <v>3</v>
       </c>
       <c r="AC71" s="10" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="58"/>
+        <v/>
+      </c>
+      <c r="AD71" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF71" s="8">
+        <v>1</v>
+      </c>
+      <c r="AG71" s="10" t="str">
+        <f t="shared" si="59"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C72" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D72" s="83" t="s">
+      <c r="D72" s="102" t="s">
         <v>53</v>
       </c>
-      <c r="E72" s="84"/>
-      <c r="F72" s="85"/>
+      <c r="E72" s="103"/>
+      <c r="F72" s="104"/>
       <c r="G72" s="72" t="s">
         <v>7</v>
       </c>
@@ -7610,8 +8474,12 @@
       <c r="AA72" s="51"/>
       <c r="AB72" s="51"/>
       <c r="AC72" s="52"/>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD72" s="83"/>
+      <c r="AE72" s="84"/>
+      <c r="AF72" s="84"/>
+      <c r="AG72" s="85"/>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B73" s="12">
         <v>46190</v>
       </c>
@@ -7693,8 +8561,21 @@
         <f>IF(ISBLANK($I73)=TRUE,"",IF(SIGN(Z73-AB73)=SIGN($G73-$I73),1,0)+IF(Z73=$G73,IF(AB73=$I73,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD73" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF73" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG73" s="11" t="str">
+        <f>IF(ISBLANK($I73)=TRUE,"",IF(SIGN(AD73-AF73)=SIGN($G73-$I73),1,0)+IF(AD73=$G73,IF(AF73=$I73,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B74" s="12">
         <v>46191</v>
       </c>
@@ -7725,7 +8606,7 @@
         <v>3</v>
       </c>
       <c r="M74" s="9" t="str">
-        <f t="shared" ref="M74:M78" si="50">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(J74-L74)=SIGN($G74-$I74),1,0)+IF(J74=$G74,IF(L74=$I74,2,0),0))</f>
+        <f t="shared" ref="M74:M78" si="60">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(J74-L74)=SIGN($G74-$I74),1,0)+IF(J74=$G74,IF(L74=$I74,2,0),0))</f>
         <v/>
       </c>
       <c r="N74" s="3">
@@ -7738,7 +8619,7 @@
         <v>2</v>
       </c>
       <c r="Q74" s="9" t="str">
-        <f t="shared" ref="Q74:Q78" si="51">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(N74-P74)=SIGN($G74-$I74),1,0)+IF(N74=$G74,IF(P74=$I74,2,0),0))</f>
+        <f t="shared" ref="Q74:Q78" si="61">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(N74-P74)=SIGN($G74-$I74),1,0)+IF(N74=$G74,IF(P74=$I74,2,0),0))</f>
         <v/>
       </c>
       <c r="R74" s="3">
@@ -7751,7 +8632,7 @@
         <v>2</v>
       </c>
       <c r="U74" s="9" t="str">
-        <f t="shared" ref="U74:U78" si="52">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(R74-T74)=SIGN($G74-$I74),1,0)+IF(R74=$G74,IF(T74=$I74,2,0),0))</f>
+        <f t="shared" ref="U74:U78" si="62">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(R74-T74)=SIGN($G74-$I74),1,0)+IF(R74=$G74,IF(T74=$I74,2,0),0))</f>
         <v/>
       </c>
       <c r="V74" s="3"/>
@@ -7760,7 +8641,7 @@
       </c>
       <c r="X74" s="7"/>
       <c r="Y74" s="9" t="str">
-        <f t="shared" ref="Y74:Y78" si="53">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(V74-X74)=SIGN($G74-$I74),1,0)+IF(V74=$G74,IF(X74=$I74,2,0),0))</f>
+        <f t="shared" ref="Y74:Y78" si="63">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(V74-X74)=SIGN($G74-$I74),1,0)+IF(V74=$G74,IF(X74=$I74,2,0),0))</f>
         <v/>
       </c>
       <c r="Z74" s="3">
@@ -7773,11 +8654,24 @@
         <v>3</v>
       </c>
       <c r="AC74" s="9" t="str">
-        <f t="shared" ref="AC74:AC78" si="54">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(Z74-AB74)=SIGN($G74-$I74),1,0)+IF(Z74=$G74,IF(AB74=$I74,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC74:AC78" si="64">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(Z74-AB74)=SIGN($G74-$I74),1,0)+IF(Z74=$G74,IF(AB74=$I74,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF74" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG74" s="9" t="str">
+        <f t="shared" ref="AG74:AG78" si="65">IF(ISBLANK($G74)=TRUE,"",IF(SIGN(AD74-AF74)=SIGN($G74-$I74),1,0)+IF(AD74=$G74,IF(AF74=$I74,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B75" s="12">
         <v>46196</v>
       </c>
@@ -7808,7 +8702,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="N75" s="3">
@@ -7821,7 +8715,7 @@
         <v>1</v>
       </c>
       <c r="Q75" s="9" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="R75" s="3">
@@ -7834,7 +8728,7 @@
         <v>0</v>
       </c>
       <c r="U75" s="9" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="V75" s="3"/>
@@ -7843,7 +8737,7 @@
       </c>
       <c r="X75" s="7"/>
       <c r="Y75" s="9" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="Z75" s="3">
@@ -7856,11 +8750,24 @@
         <v>0</v>
       </c>
       <c r="AC75" s="9" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="64"/>
+        <v/>
+      </c>
+      <c r="AD75" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF75" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="9" t="str">
+        <f t="shared" si="65"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B76" s="12">
         <v>46197</v>
       </c>
@@ -7891,7 +8798,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="N76" s="3">
@@ -7904,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="Q76" s="9" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="R76" s="3">
@@ -7917,7 +8824,7 @@
         <v>1</v>
       </c>
       <c r="U76" s="9" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="V76" s="3"/>
@@ -7926,7 +8833,7 @@
       </c>
       <c r="X76" s="7"/>
       <c r="Y76" s="9" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="Z76" s="3">
@@ -7939,11 +8846,24 @@
         <v>2</v>
       </c>
       <c r="AC76" s="9" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="64"/>
+        <v/>
+      </c>
+      <c r="AD76" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE76" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF76" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="9" t="str">
+        <f t="shared" si="65"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B77" s="12">
         <v>46201</v>
       </c>
@@ -7974,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="M77" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="N77" s="3">
@@ -7987,7 +8907,7 @@
         <v>2</v>
       </c>
       <c r="Q77" s="9" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="R77" s="3">
@@ -8000,7 +8920,7 @@
         <v>1</v>
       </c>
       <c r="U77" s="9" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="V77" s="3"/>
@@ -8009,7 +8929,7 @@
       </c>
       <c r="X77" s="7"/>
       <c r="Y77" s="9" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="Z77" s="3">
@@ -8022,11 +8942,24 @@
         <v>1</v>
       </c>
       <c r="AC77" s="9" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="64"/>
+        <v/>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF77" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="9" t="str">
+        <f t="shared" si="65"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="13">
         <v>46201</v>
       </c>
@@ -8057,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="N78" s="4">
@@ -8070,7 +9003,7 @@
         <v>1</v>
       </c>
       <c r="Q78" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="R78" s="4">
@@ -8083,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="V78" s="4"/>
@@ -8092,7 +9025,7 @@
       </c>
       <c r="X78" s="8"/>
       <c r="Y78" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="Z78" s="4">
@@ -8105,22 +9038,35 @@
         <v>0</v>
       </c>
       <c r="AC78" s="10" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="64"/>
+        <v/>
+      </c>
+      <c r="AD78" s="4">
+        <v>3</v>
+      </c>
+      <c r="AE78" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF78" s="8">
+        <v>1</v>
+      </c>
+      <c r="AG78" s="10" t="str">
+        <f t="shared" si="65"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C79" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D79" s="83" t="s">
+      <c r="D79" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="E79" s="84"/>
-      <c r="F79" s="85"/>
+      <c r="E79" s="103"/>
+      <c r="F79" s="104"/>
       <c r="G79" s="72" t="s">
         <v>7</v>
       </c>
@@ -8146,8 +9092,12 @@
       <c r="AA79" s="51"/>
       <c r="AB79" s="51"/>
       <c r="AC79" s="52"/>
-    </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD79" s="83"/>
+      <c r="AE79" s="84"/>
+      <c r="AF79" s="84"/>
+      <c r="AG79" s="85"/>
+    </row>
+    <row r="80" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B80" s="12">
         <v>46190</v>
       </c>
@@ -8229,8 +9179,21 @@
         <f>IF(ISBLANK($I80)=TRUE,"",IF(SIGN(Z80-AB80)=SIGN($G80-$I80),1,0)+IF(Z80=$G80,IF(AB80=$I80,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="81" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD80" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE80" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF80" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="11" t="str">
+        <f>IF(ISBLANK($I80)=TRUE,"",IF(SIGN(AD80-AF80)=SIGN($G80-$I80),1,0)+IF(AD80=$G80,IF(AF80=$I80,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B81" s="12">
         <v>46191</v>
       </c>
@@ -8261,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="9" t="str">
-        <f t="shared" ref="M81:M85" si="55">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(J81-L81)=SIGN($G81-$I81),1,0)+IF(J81=$G81,IF(L81=$I81,2,0),0))</f>
+        <f t="shared" ref="M81:M85" si="66">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(J81-L81)=SIGN($G81-$I81),1,0)+IF(J81=$G81,IF(L81=$I81,2,0),0))</f>
         <v/>
       </c>
       <c r="N81" s="3">
@@ -8274,7 +9237,7 @@
         <v>1</v>
       </c>
       <c r="Q81" s="9" t="str">
-        <f t="shared" ref="Q81:Q85" si="56">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(N81-P81)=SIGN($G81-$I81),1,0)+IF(N81=$G81,IF(P81=$I81,2,0),0))</f>
+        <f t="shared" ref="Q81:Q85" si="67">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(N81-P81)=SIGN($G81-$I81),1,0)+IF(N81=$G81,IF(P81=$I81,2,0),0))</f>
         <v/>
       </c>
       <c r="R81" s="3">
@@ -8287,7 +9250,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="9" t="str">
-        <f t="shared" ref="U81:U85" si="57">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(R81-T81)=SIGN($G81-$I81),1,0)+IF(R81=$G81,IF(T81=$I81,2,0),0))</f>
+        <f t="shared" ref="U81:U85" si="68">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(R81-T81)=SIGN($G81-$I81),1,0)+IF(R81=$G81,IF(T81=$I81,2,0),0))</f>
         <v/>
       </c>
       <c r="V81" s="3"/>
@@ -8296,7 +9259,7 @@
       </c>
       <c r="X81" s="7"/>
       <c r="Y81" s="9" t="str">
-        <f t="shared" ref="Y81:Y85" si="58">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(V81-X81)=SIGN($G81-$I81),1,0)+IF(V81=$G81,IF(X81=$I81,2,0),0))</f>
+        <f t="shared" ref="Y81:Y85" si="69">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(V81-X81)=SIGN($G81-$I81),1,0)+IF(V81=$G81,IF(X81=$I81,2,0),0))</f>
         <v/>
       </c>
       <c r="Z81" s="3">
@@ -8309,11 +9272,24 @@
         <v>0</v>
       </c>
       <c r="AC81" s="9" t="str">
-        <f t="shared" ref="AC81:AC85" si="59">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(Z81-AB81)=SIGN($G81-$I81),1,0)+IF(Z81=$G81,IF(AB81=$I81,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC81:AC85" si="70">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(Z81-AB81)=SIGN($G81-$I81),1,0)+IF(Z81=$G81,IF(AB81=$I81,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD81" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE81" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF81" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="9" t="str">
+        <f t="shared" ref="AG81:AG85" si="71">IF(ISBLANK($G81)=TRUE,"",IF(SIGN(AD81-AF81)=SIGN($G81-$I81),1,0)+IF(AD81=$G81,IF(AF81=$I81,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B82" s="12">
         <v>46196</v>
       </c>
@@ -8344,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="9" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="N82" s="3">
@@ -8357,7 +9333,7 @@
         <v>1</v>
       </c>
       <c r="Q82" s="9" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="R82" s="3">
@@ -8370,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="U82" s="9" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="V82" s="3"/>
@@ -8379,7 +9355,7 @@
       </c>
       <c r="X82" s="7"/>
       <c r="Y82" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="Z82" s="3">
@@ -8392,11 +9368,24 @@
         <v>0</v>
       </c>
       <c r="AC82" s="9" t="str">
-        <f t="shared" si="59"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="70"/>
+        <v/>
+      </c>
+      <c r="AD82" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF82" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG82" s="9" t="str">
+        <f t="shared" si="71"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B83" s="12">
         <v>46197</v>
       </c>
@@ -8427,7 +9416,7 @@
         <v>2</v>
       </c>
       <c r="M83" s="9" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="N83" s="3">
@@ -8440,7 +9429,7 @@
         <v>2</v>
       </c>
       <c r="Q83" s="9" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="R83" s="3">
@@ -8453,7 +9442,7 @@
         <v>2</v>
       </c>
       <c r="U83" s="9" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="V83" s="3"/>
@@ -8462,7 +9451,7 @@
       </c>
       <c r="X83" s="7"/>
       <c r="Y83" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="Z83" s="3">
@@ -8475,11 +9464,24 @@
         <v>1</v>
       </c>
       <c r="AC83" s="9" t="str">
-        <f t="shared" si="59"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="70"/>
+        <v/>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF83" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG83" s="9" t="str">
+        <f t="shared" si="71"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B84" s="12">
         <v>46200</v>
       </c>
@@ -8510,7 +9512,7 @@
         <v>3</v>
       </c>
       <c r="M84" s="9" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="N84" s="3">
@@ -8523,7 +9525,7 @@
         <v>2</v>
       </c>
       <c r="Q84" s="9" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="R84" s="3">
@@ -8536,7 +9538,7 @@
         <v>2</v>
       </c>
       <c r="U84" s="9" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="V84" s="3"/>
@@ -8545,7 +9547,7 @@
       </c>
       <c r="X84" s="7"/>
       <c r="Y84" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="Z84" s="3">
@@ -8558,11 +9560,24 @@
         <v>1</v>
       </c>
       <c r="AC84" s="9" t="str">
-        <f t="shared" si="59"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="70"/>
+        <v/>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF84" s="7">
+        <v>3</v>
+      </c>
+      <c r="AG84" s="9" t="str">
+        <f t="shared" si="71"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="13">
         <v>46200</v>
       </c>
@@ -8593,7 +9608,7 @@
         <v>0</v>
       </c>
       <c r="M85" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="N85" s="4">
@@ -8606,7 +9621,7 @@
         <v>2</v>
       </c>
       <c r="Q85" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="R85" s="4">
@@ -8619,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="U85" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="V85" s="4"/>
@@ -8628,7 +9643,7 @@
       </c>
       <c r="X85" s="8"/>
       <c r="Y85" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="Z85" s="4">
@@ -8641,164 +9656,185 @@
         <v>0</v>
       </c>
       <c r="AC85" s="10" t="str">
-        <f t="shared" si="59"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="86" t="s">
+        <f t="shared" si="70"/>
+        <v/>
+      </c>
+      <c r="AD85" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE85" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF85" s="8">
+        <v>1</v>
+      </c>
+      <c r="AG85" s="10" t="str">
+        <f t="shared" si="71"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="105" t="s">
         <v>127</v>
       </c>
-      <c r="C86" s="87"/>
-      <c r="D86" s="87"/>
-      <c r="E86" s="87"/>
-      <c r="F86" s="87"/>
-      <c r="G86" s="87"/>
-      <c r="H86" s="87"/>
-      <c r="I86" s="88"/>
-      <c r="J86" s="89">
+      <c r="C86" s="106"/>
+      <c r="D86" s="106"/>
+      <c r="E86" s="106"/>
+      <c r="F86" s="106"/>
+      <c r="G86" s="106"/>
+      <c r="H86" s="106"/>
+      <c r="I86" s="107"/>
+      <c r="J86" s="108">
         <f>SUM(M3:M85)</f>
         <v>0</v>
       </c>
-      <c r="K86" s="90"/>
-      <c r="L86" s="90"/>
-      <c r="M86" s="91"/>
-      <c r="N86" s="92">
+      <c r="K86" s="109"/>
+      <c r="L86" s="109"/>
+      <c r="M86" s="110"/>
+      <c r="N86" s="111">
         <f>SUM(Q3:Q85)</f>
         <v>0</v>
       </c>
-      <c r="O86" s="93"/>
-      <c r="P86" s="93"/>
-      <c r="Q86" s="94"/>
-      <c r="R86" s="98">
+      <c r="O86" s="112"/>
+      <c r="P86" s="112"/>
+      <c r="Q86" s="113"/>
+      <c r="R86" s="117">
         <f>SUM(U3:U85)</f>
         <v>0</v>
       </c>
-      <c r="S86" s="99"/>
-      <c r="T86" s="99"/>
-      <c r="U86" s="100"/>
-      <c r="V86" s="101">
+      <c r="S86" s="118"/>
+      <c r="T86" s="118"/>
+      <c r="U86" s="119"/>
+      <c r="V86" s="120">
         <f>SUM(Y3:Y85)</f>
         <v>0</v>
       </c>
-      <c r="W86" s="102"/>
-      <c r="X86" s="102"/>
-      <c r="Y86" s="103"/>
-      <c r="Z86" s="95">
+      <c r="W86" s="121"/>
+      <c r="X86" s="121"/>
+      <c r="Y86" s="122"/>
+      <c r="Z86" s="114">
         <f>SUM(AC3:AC85)</f>
         <v>0</v>
       </c>
-      <c r="AA86" s="96"/>
-      <c r="AB86" s="96"/>
-      <c r="AC86" s="97"/>
-    </row>
-    <row r="87" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AA86" s="115"/>
+      <c r="AB86" s="115"/>
+      <c r="AC86" s="116"/>
+      <c r="AD86" s="99">
+        <f>SUM(AG3:AG85)</f>
+        <v>0</v>
+      </c>
+      <c r="AE86" s="100"/>
+      <c r="AF86" s="100"/>
+      <c r="AG86" s="101"/>
+    </row>
+    <row r="87" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E87" s="47"/>
     </row>
-    <row r="88" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E88" s="47"/>
     </row>
-    <row r="89" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E89" s="47"/>
     </row>
-    <row r="90" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E90" s="47"/>
     </row>
-    <row r="91" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E91" s="47"/>
     </row>
-    <row r="92" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E92" s="47"/>
     </row>
-    <row r="93" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E93" s="47"/>
     </row>
-    <row r="94" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E94" s="47"/>
     </row>
-    <row r="95" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E95" s="47"/>
     </row>
-    <row r="96" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E96" s="47"/>
     </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E97" s="47"/>
     </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E98" s="47"/>
     </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E99" s="47"/>
     </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E100" s="47"/>
     </row>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E101" s="47"/>
     </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E102" s="47"/>
     </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E103" s="47"/>
     </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E104" s="47"/>
     </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E105" s="47"/>
     </row>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E106" s="47"/>
     </row>
-    <row r="107" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E107" s="47"/>
     </row>
-    <row r="108" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E108" s="47"/>
     </row>
-    <row r="109" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E109" s="47"/>
     </row>
-    <row r="110" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E110" s="47"/>
     </row>
-    <row r="111" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E111" s="47"/>
     </row>
-    <row r="112" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E112" s="47"/>
     </row>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E113" s="47"/>
     </row>
-    <row r="114" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E114" s="47"/>
     </row>
-    <row r="115" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E115" s="47"/>
     </row>
-    <row r="116" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E116" s="47"/>
     </row>
-    <row r="117" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E117" s="47"/>
     </row>
-    <row r="118" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E118" s="47"/>
     </row>
-    <row r="119" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E119" s="47"/>
     </row>
-    <row r="120" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E120" s="47"/>
     </row>
-    <row r="121" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E121" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
+    <mergeCell ref="D9:F9"/>
     <mergeCell ref="N2:Q2"/>
     <mergeCell ref="N86:Q86"/>
     <mergeCell ref="Z2:AC2"/>
@@ -8807,13 +9843,8 @@
     <mergeCell ref="R86:U86"/>
     <mergeCell ref="V2:Y2"/>
     <mergeCell ref="V86:Y86"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="AD2:AG2"/>
+    <mergeCell ref="AD86:AG86"/>
     <mergeCell ref="D51:F51"/>
     <mergeCell ref="B86:I86"/>
     <mergeCell ref="J86:M86"/>
@@ -8822,6 +9853,12 @@
     <mergeCell ref="D58:F58"/>
     <mergeCell ref="D79:F79"/>
     <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="D16:F16"/>
   </mergeCells>
   <conditionalFormatting sqref="M3:M8 M10:M15 M17:M22 M24:M29 M31:M36 M38:M43 M45:M50 M52:M57 M59:M64 M66:M71 M73:M78 M80:M85">
     <cfRule type="colorScale" priority="8">
@@ -8863,7 +9900,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC3:AC8 AC80:AC85 AC10:AC15 AC17:AC22 AC24:AC29 AC31:AC36 AC38:AC43 AC45:AC50 AC52:AC57 AC59:AC64 AC66:AC71 AC73:AC78">
+  <conditionalFormatting sqref="AC3:AC8 AC80:AC85 AC10:AC15 AC17:AC22 AC24:AC29 AC31:AC36 AC38:AC43 AC45:AC50 AC52:AC57 AC59:AC64 AC66:AC71 AC73:AC78 AG3:AG8 AG80:AG85 AG10:AG15 AG17:AG22 AG24:AG29 AG31:AG36 AG38:AG43 AG45:AG50 AG52:AG57 AG59:AG64 AG66:AG71 AG73:AG78">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -8879,91 +9916,101 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBE0114-FB52-48EB-B9E8-BE1CEF0426EF}">
-  <dimension ref="B1:AC58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:AG58"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="47" customWidth="1"/>
-    <col min="2" max="2" width="7.109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.88671875" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" style="49" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.88671875" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.5546875" style="47" customWidth="1"/>
-    <col min="8" max="8" width="1.44140625" style="47" customWidth="1"/>
-    <col min="9" max="9" width="3.5546875" style="47" customWidth="1"/>
-    <col min="10" max="10" width="3.109375" style="47" customWidth="1"/>
-    <col min="11" max="11" width="1.44140625" style="47" customWidth="1"/>
-    <col min="12" max="12" width="3.109375" style="47" customWidth="1"/>
-    <col min="13" max="13" width="2.88671875" style="47" customWidth="1"/>
-    <col min="14" max="14" width="3.109375" style="47" customWidth="1"/>
-    <col min="15" max="15" width="1.44140625" style="47" customWidth="1"/>
-    <col min="16" max="16" width="3.109375" style="47" customWidth="1"/>
-    <col min="17" max="17" width="2.88671875" style="47" customWidth="1"/>
-    <col min="18" max="18" width="3.109375" style="47" customWidth="1"/>
-    <col min="19" max="19" width="1.44140625" style="47" customWidth="1"/>
-    <col min="20" max="20" width="3.109375" style="47" customWidth="1"/>
-    <col min="21" max="21" width="2.88671875" style="47" customWidth="1"/>
-    <col min="22" max="22" width="3.109375" style="47" customWidth="1"/>
-    <col min="23" max="23" width="1.44140625" style="47" customWidth="1"/>
-    <col min="24" max="24" width="3.109375" style="47" customWidth="1"/>
-    <col min="25" max="25" width="2.88671875" style="47" customWidth="1"/>
-    <col min="26" max="26" width="3.109375" style="47" customWidth="1"/>
-    <col min="27" max="27" width="1.44140625" style="47" customWidth="1"/>
-    <col min="28" max="28" width="3.109375" style="47" customWidth="1"/>
-    <col min="29" max="29" width="2.88671875" style="47" customWidth="1"/>
-    <col min="30" max="16384" width="11.44140625" style="47"/>
+    <col min="2" max="2" width="7.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" style="49" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" style="47" customWidth="1"/>
+    <col min="8" max="8" width="1.42578125" style="47" customWidth="1"/>
+    <col min="9" max="9" width="3.5703125" style="47" customWidth="1"/>
+    <col min="10" max="10" width="3.140625" style="47" customWidth="1"/>
+    <col min="11" max="11" width="1.42578125" style="47" customWidth="1"/>
+    <col min="12" max="12" width="3.140625" style="47" customWidth="1"/>
+    <col min="13" max="13" width="2.85546875" style="47" customWidth="1"/>
+    <col min="14" max="14" width="3.140625" style="47" customWidth="1"/>
+    <col min="15" max="15" width="1.42578125" style="47" customWidth="1"/>
+    <col min="16" max="16" width="3.140625" style="47" customWidth="1"/>
+    <col min="17" max="17" width="2.85546875" style="47" customWidth="1"/>
+    <col min="18" max="18" width="3.140625" style="47" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="47" customWidth="1"/>
+    <col min="20" max="20" width="3.140625" style="47" customWidth="1"/>
+    <col min="21" max="21" width="2.85546875" style="47" customWidth="1"/>
+    <col min="22" max="22" width="3.140625" style="47" customWidth="1"/>
+    <col min="23" max="23" width="1.42578125" style="47" customWidth="1"/>
+    <col min="24" max="24" width="3.140625" style="47" customWidth="1"/>
+    <col min="25" max="25" width="2.85546875" style="47" customWidth="1"/>
+    <col min="26" max="26" width="3.140625" style="47" customWidth="1"/>
+    <col min="27" max="27" width="1.42578125" style="47" customWidth="1"/>
+    <col min="28" max="28" width="3.140625" style="47" customWidth="1"/>
+    <col min="29" max="29" width="2.85546875" style="47" customWidth="1"/>
+    <col min="30" max="30" width="3.140625" style="47" customWidth="1"/>
+    <col min="31" max="31" width="1.42578125" style="47" customWidth="1"/>
+    <col min="32" max="32" width="3.140625" style="47" customWidth="1"/>
+    <col min="33" max="33" width="2.85546875" style="47" customWidth="1"/>
+    <col min="34" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="75" t="s">
         <v>77</v>
       </c>
       <c r="C2" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="104" t="s">
+      <c r="D2" s="123" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="106"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="125"/>
       <c r="G2" s="72" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="73"/>
       <c r="I2" s="74"/>
-      <c r="J2" s="89" t="s">
+      <c r="J2" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="92" t="s">
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="111" t="s">
         <v>139</v>
       </c>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-      <c r="Q2" s="94"/>
-      <c r="R2" s="98" t="s">
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="100"/>
-      <c r="V2" s="101" t="s">
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
+      <c r="U2" s="119"/>
+      <c r="V2" s="120" t="s">
         <v>140</v>
       </c>
-      <c r="W2" s="102"/>
-      <c r="X2" s="102"/>
-      <c r="Y2" s="103"/>
-      <c r="Z2" s="95" t="s">
+      <c r="W2" s="121"/>
+      <c r="X2" s="121"/>
+      <c r="Y2" s="122"/>
+      <c r="Z2" s="114" t="s">
         <v>138</v>
       </c>
-      <c r="AA2" s="96"/>
-      <c r="AB2" s="96"/>
-      <c r="AC2" s="97"/>
-    </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AA2" s="115"/>
+      <c r="AB2" s="115"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="99" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE2" s="100"/>
+      <c r="AF2" s="100"/>
+      <c r="AG2" s="101"/>
+    </row>
+    <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="25">
         <v>46201</v>
       </c>
@@ -9025,8 +10072,17 @@
         <f>IF(ISBLANK($I3)=TRUE,"",IF(SIGN(Z3-AB3)=SIGN($G3-$I3),1,0)+IF(Z3=$G3,IF(AB3=$I3,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="29"/>
+      <c r="AG3" s="11" t="str">
+        <f>IF(ISBLANK($I3)=TRUE,"",IF(SIGN(AD3-AF3)=SIGN($G3-$I3),1,0)+IF(AD3=$G3,IF(AF3=$I3,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="12">
         <v>46202</v>
       </c>
@@ -9088,8 +10144,17 @@
         <f t="shared" ref="AC4:AC12" si="4">IF(ISBLANK($G4)=TRUE,"",IF(SIGN(Z4-AB4)=SIGN($G4-$I4),1,0)+IF(Z4=$G4,IF(AB4=$I4,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="9" t="str">
+        <f t="shared" ref="AG4:AG12" si="5">IF(ISBLANK($G4)=TRUE,"",IF(SIGN(AD4-AF4)=SIGN($G4-$I4),1,0)+IF(AD4=$G4,IF(AF4=$I4,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="12">
         <v>46202</v>
       </c>
@@ -9151,8 +10216,17 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="12">
         <v>46203</v>
       </c>
@@ -9214,8 +10288,17 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="12">
         <v>46203</v>
       </c>
@@ -9277,8 +10360,17 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="12">
         <v>46203</v>
       </c>
@@ -9301,7 +10393,7 @@
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="9" t="str">
-        <f t="shared" ref="M8:M11" si="5">IF(ISBLANK($G8)=TRUE,"",IF(SIGN(J8-L8)=SIGN($G8-$I8),1,0)+IF(J8=$G8,IF(L8=$I8,2,0),0))</f>
+        <f t="shared" ref="M8:M11" si="6">IF(ISBLANK($G8)=TRUE,"",IF(SIGN(J8-L8)=SIGN($G8-$I8),1,0)+IF(J8=$G8,IF(L8=$I8,2,0),0))</f>
         <v/>
       </c>
       <c r="N8" s="3"/>
@@ -9340,8 +10432,17 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="12">
         <v>46204</v>
       </c>
@@ -9364,7 +10465,7 @@
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N9" s="3"/>
@@ -9403,8 +10504,17 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="12">
         <v>46204</v>
       </c>
@@ -9427,7 +10537,7 @@
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N10" s="3"/>
@@ -9466,8 +10576,17 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="12">
         <v>46204</v>
       </c>
@@ -9490,7 +10609,7 @@
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N11" s="3"/>
@@ -9529,8 +10648,17 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="5"/>
+      <c r="AG11" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="12">
         <v>46205</v>
       </c>
@@ -9592,8 +10720,17 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>46205</v>
       </c>
@@ -9655,8 +10792,17 @@
         <f>IF(ISBLANK($I13)=TRUE,"",IF(SIGN(Z13-AB13)=SIGN($G13-$I13),1,0)+IF(Z13=$G13,IF(AB13=$I13,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="5"/>
+      <c r="AG13" s="9" t="str">
+        <f>IF(ISBLANK($I13)=TRUE,"",IF(SIGN(AD13-AF13)=SIGN($G13-$I13),1,0)+IF(AD13=$G13,IF(AF13=$I13,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="12">
         <v>46206</v>
       </c>
@@ -9679,7 +10825,7 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="9" t="str">
-        <f t="shared" ref="M14:M18" si="6">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(J14-L14)=SIGN($G14-$I14),1,0)+IF(J14=$G14,IF(L14=$I14,2,0),0))</f>
+        <f t="shared" ref="M14:M18" si="7">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(J14-L14)=SIGN($G14-$I14),1,0)+IF(J14=$G14,IF(L14=$I14,2,0),0))</f>
         <v/>
       </c>
       <c r="N14" s="3"/>
@@ -9688,7 +10834,7 @@
       </c>
       <c r="P14" s="5"/>
       <c r="Q14" s="9" t="str">
-        <f t="shared" ref="Q14:Q18" si="7">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(N14-P14)=SIGN($G14-$I14),1,0)+IF(N14=$G14,IF(P14=$I14,2,0),0))</f>
+        <f t="shared" ref="Q14:Q18" si="8">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(N14-P14)=SIGN($G14-$I14),1,0)+IF(N14=$G14,IF(P14=$I14,2,0),0))</f>
         <v/>
       </c>
       <c r="R14" s="3"/>
@@ -9697,7 +10843,7 @@
       </c>
       <c r="T14" s="5"/>
       <c r="U14" s="9" t="str">
-        <f t="shared" ref="U14:U18" si="8">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(R14-T14)=SIGN($G14-$I14),1,0)+IF(R14=$G14,IF(T14=$I14,2,0),0))</f>
+        <f t="shared" ref="U14:U18" si="9">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(R14-T14)=SIGN($G14-$I14),1,0)+IF(R14=$G14,IF(T14=$I14,2,0),0))</f>
         <v/>
       </c>
       <c r="V14" s="3"/>
@@ -9706,7 +10852,7 @@
       </c>
       <c r="X14" s="5"/>
       <c r="Y14" s="9" t="str">
-        <f t="shared" ref="Y14:Y18" si="9">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(V14-X14)=SIGN($G14-$I14),1,0)+IF(V14=$G14,IF(X14=$I14,2,0),0))</f>
+        <f t="shared" ref="Y14:Y18" si="10">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(V14-X14)=SIGN($G14-$I14),1,0)+IF(V14=$G14,IF(X14=$I14,2,0),0))</f>
         <v/>
       </c>
       <c r="Z14" s="3"/>
@@ -9715,11 +10861,20 @@
       </c>
       <c r="AB14" s="5"/>
       <c r="AC14" s="9" t="str">
-        <f t="shared" ref="AC14:AC18" si="10">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(Z14-AB14)=SIGN($G14-$I14),1,0)+IF(Z14=$G14,IF(AB14=$I14,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC14:AC18" si="11">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(Z14-AB14)=SIGN($G14-$I14),1,0)+IF(Z14=$G14,IF(AB14=$I14,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="9" t="str">
+        <f t="shared" ref="AG14:AG18" si="12">IF(ISBLANK($G14)=TRUE,"",IF(SIGN(AD14-AF14)=SIGN($G14-$I14),1,0)+IF(AD14=$G14,IF(AF14=$I14,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>46206</v>
       </c>
@@ -9742,7 +10897,7 @@
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N15" s="3"/>
@@ -9751,7 +10906,7 @@
       </c>
       <c r="P15" s="5"/>
       <c r="Q15" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R15" s="3"/>
@@ -9760,7 +10915,7 @@
       </c>
       <c r="T15" s="5"/>
       <c r="U15" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="V15" s="3"/>
@@ -9769,7 +10924,7 @@
       </c>
       <c r="X15" s="5"/>
       <c r="Y15" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="Z15" s="3"/>
@@ -9778,11 +10933,20 @@
       </c>
       <c r="AB15" s="5"/>
       <c r="AC15" s="9" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="12">
         <v>46206</v>
       </c>
@@ -9805,7 +10969,7 @@
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N16" s="3"/>
@@ -9814,7 +10978,7 @@
       </c>
       <c r="P16" s="5"/>
       <c r="Q16" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R16" s="3"/>
@@ -9823,7 +10987,7 @@
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="V16" s="3"/>
@@ -9832,7 +10996,7 @@
       </c>
       <c r="X16" s="5"/>
       <c r="Y16" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="Z16" s="3"/>
@@ -9841,11 +11005,20 @@
       </c>
       <c r="AB16" s="5"/>
       <c r="AC16" s="9" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="5"/>
+      <c r="AG16" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="12">
         <v>46207</v>
       </c>
@@ -9868,7 +11041,7 @@
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N17" s="3"/>
@@ -9877,7 +11050,7 @@
       </c>
       <c r="P17" s="5"/>
       <c r="Q17" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R17" s="3"/>
@@ -9886,7 +11059,7 @@
       </c>
       <c r="T17" s="5"/>
       <c r="U17" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="V17" s="3"/>
@@ -9895,7 +11068,7 @@
       </c>
       <c r="X17" s="5"/>
       <c r="Y17" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="Z17" s="3"/>
@@ -9904,11 +11077,20 @@
       </c>
       <c r="AB17" s="5"/>
       <c r="AC17" s="9" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="5"/>
+      <c r="AG17" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="13">
         <v>46207</v>
       </c>
@@ -9931,7 +11113,7 @@
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N18" s="4"/>
@@ -9940,7 +11122,7 @@
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R18" s="4"/>
@@ -9949,7 +11131,7 @@
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="V18" s="4"/>
@@ -9958,7 +11140,7 @@
       </c>
       <c r="X18" s="6"/>
       <c r="Y18" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="Z18" s="4"/>
@@ -9967,22 +11149,31 @@
       </c>
       <c r="AB18" s="6"/>
       <c r="AC18" s="10" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AD18" s="4"/>
+      <c r="AE18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="6"/>
+      <c r="AG18" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="75" t="s">
         <v>77</v>
       </c>
       <c r="C19" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="104" t="s">
+      <c r="D19" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="E19" s="105"/>
-      <c r="F19" s="106"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="125"/>
       <c r="G19" s="72" t="s">
         <v>7</v>
       </c>
@@ -10008,8 +11199,12 @@
       <c r="AA19" s="51"/>
       <c r="AB19" s="51"/>
       <c r="AC19" s="52"/>
-    </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD19" s="83"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="85"/>
+    </row>
+    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="25">
         <v>46207</v>
       </c>
@@ -10071,8 +11266,17 @@
         <f>IF(ISBLANK($I20)=TRUE,"",IF(SIGN(Z20-AB20)=SIGN($G20-$I20),1,0)+IF(Z20=$G20,IF(AB20=$I20,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD20" s="27"/>
+      <c r="AE20" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="29"/>
+      <c r="AG20" s="11" t="str">
+        <f>IF(ISBLANK($I20)=TRUE,"",IF(SIGN(AD20-AF20)=SIGN($G20-$I20),1,0)+IF(AD20=$G20,IF(AF20=$I20,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="12">
         <v>46207</v>
       </c>
@@ -10095,7 +11299,7 @@
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="9" t="str">
-        <f t="shared" ref="M21:M27" si="11">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(J21-L21)=SIGN($G21-$I21),1,0)+IF(J21=$G21,IF(L21=$I21,2,0),0))</f>
+        <f t="shared" ref="M21:M27" si="13">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(J21-L21)=SIGN($G21-$I21),1,0)+IF(J21=$G21,IF(L21=$I21,2,0),0))</f>
         <v/>
       </c>
       <c r="N21" s="3"/>
@@ -10104,7 +11308,7 @@
       </c>
       <c r="P21" s="5"/>
       <c r="Q21" s="9" t="str">
-        <f t="shared" ref="Q21:Q27" si="12">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(N21-P21)=SIGN($G21-$I21),1,0)+IF(N21=$G21,IF(P21=$I21,2,0),0))</f>
+        <f t="shared" ref="Q21:Q27" si="14">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(N21-P21)=SIGN($G21-$I21),1,0)+IF(N21=$G21,IF(P21=$I21,2,0),0))</f>
         <v/>
       </c>
       <c r="R21" s="3"/>
@@ -10113,7 +11317,7 @@
       </c>
       <c r="T21" s="5"/>
       <c r="U21" s="9" t="str">
-        <f t="shared" ref="U21:U27" si="13">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(R21-T21)=SIGN($G21-$I21),1,0)+IF(R21=$G21,IF(T21=$I21,2,0),0))</f>
+        <f t="shared" ref="U21:U27" si="15">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(R21-T21)=SIGN($G21-$I21),1,0)+IF(R21=$G21,IF(T21=$I21,2,0),0))</f>
         <v/>
       </c>
       <c r="V21" s="3"/>
@@ -10122,7 +11326,7 @@
       </c>
       <c r="X21" s="5"/>
       <c r="Y21" s="9" t="str">
-        <f t="shared" ref="Y21:Y27" si="14">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(V21-X21)=SIGN($G21-$I21),1,0)+IF(V21=$G21,IF(X21=$I21,2,0),0))</f>
+        <f t="shared" ref="Y21:Y27" si="16">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(V21-X21)=SIGN($G21-$I21),1,0)+IF(V21=$G21,IF(X21=$I21,2,0),0))</f>
         <v/>
       </c>
       <c r="Z21" s="3"/>
@@ -10131,11 +11335,20 @@
       </c>
       <c r="AB21" s="5"/>
       <c r="AC21" s="9" t="str">
-        <f t="shared" ref="AC21:AC27" si="15">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(Z21-AB21)=SIGN($G21-$I21),1,0)+IF(Z21=$G21,IF(AB21=$I21,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC21:AC27" si="17">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(Z21-AB21)=SIGN($G21-$I21),1,0)+IF(Z21=$G21,IF(AB21=$I21,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="9" t="str">
+        <f t="shared" ref="AG21:AG27" si="18">IF(ISBLANK($G21)=TRUE,"",IF(SIGN(AD21-AF21)=SIGN($G21-$I21),1,0)+IF(AD21=$G21,IF(AF21=$I21,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="12">
         <v>46208</v>
       </c>
@@ -10158,7 +11371,7 @@
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="9" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N22" s="3"/>
@@ -10167,7 +11380,7 @@
       </c>
       <c r="P22" s="5"/>
       <c r="Q22" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R22" s="3"/>
@@ -10176,7 +11389,7 @@
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="V22" s="3"/>
@@ -10185,7 +11398,7 @@
       </c>
       <c r="X22" s="5"/>
       <c r="Y22" s="9" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Z22" s="3"/>
@@ -10194,11 +11407,20 @@
       </c>
       <c r="AB22" s="5"/>
       <c r="AC22" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="5"/>
+      <c r="AG22" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" s="12">
         <v>46209</v>
       </c>
@@ -10221,7 +11443,7 @@
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="9" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N23" s="3"/>
@@ -10230,7 +11452,7 @@
       </c>
       <c r="P23" s="5"/>
       <c r="Q23" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R23" s="3"/>
@@ -10239,7 +11461,7 @@
       </c>
       <c r="T23" s="5"/>
       <c r="U23" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="V23" s="3"/>
@@ -10248,7 +11470,7 @@
       </c>
       <c r="X23" s="5"/>
       <c r="Y23" s="9" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Z23" s="3"/>
@@ -10257,11 +11479,20 @@
       </c>
       <c r="AB23" s="5"/>
       <c r="AC23" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF23" s="5"/>
+      <c r="AG23" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" s="12">
         <v>46209</v>
       </c>
@@ -10284,7 +11515,7 @@
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="9" t="str">
-        <f t="shared" ref="M24:M26" si="16">IF(ISBLANK($G24)=TRUE,"",IF(SIGN(J24-L24)=SIGN($G24-$I24),1,0)+IF(J24=$G24,IF(L24=$I24,2,0),0))</f>
+        <f t="shared" ref="M24:M26" si="19">IF(ISBLANK($G24)=TRUE,"",IF(SIGN(J24-L24)=SIGN($G24-$I24),1,0)+IF(J24=$G24,IF(L24=$I24,2,0),0))</f>
         <v/>
       </c>
       <c r="N24" s="3"/>
@@ -10293,7 +11524,7 @@
       </c>
       <c r="P24" s="5"/>
       <c r="Q24" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R24" s="3"/>
@@ -10302,7 +11533,7 @@
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="V24" s="3"/>
@@ -10311,7 +11542,7 @@
       </c>
       <c r="X24" s="5"/>
       <c r="Y24" s="9" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Z24" s="3"/>
@@ -10320,11 +11551,20 @@
       </c>
       <c r="AB24" s="5"/>
       <c r="AC24" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="5"/>
+      <c r="AG24" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" s="12">
         <v>46210</v>
       </c>
@@ -10347,7 +11587,7 @@
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="9" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="N25" s="3"/>
@@ -10356,7 +11596,7 @@
       </c>
       <c r="P25" s="5"/>
       <c r="Q25" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R25" s="3"/>
@@ -10365,7 +11605,7 @@
       </c>
       <c r="T25" s="5"/>
       <c r="U25" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="V25" s="3"/>
@@ -10374,7 +11614,7 @@
       </c>
       <c r="X25" s="5"/>
       <c r="Y25" s="9" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Z25" s="3"/>
@@ -10383,11 +11623,20 @@
       </c>
       <c r="AB25" s="5"/>
       <c r="AC25" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="5"/>
+      <c r="AG25" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" s="12">
         <v>46210</v>
       </c>
@@ -10410,7 +11659,7 @@
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="9" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="N26" s="3"/>
@@ -10419,7 +11668,7 @@
       </c>
       <c r="P26" s="5"/>
       <c r="Q26" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R26" s="3"/>
@@ -10428,7 +11677,7 @@
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="V26" s="3"/>
@@ -10437,7 +11686,7 @@
       </c>
       <c r="X26" s="5"/>
       <c r="Y26" s="9" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Z26" s="3"/>
@@ -10446,11 +11695,20 @@
       </c>
       <c r="AB26" s="5"/>
       <c r="AC26" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF26" s="5"/>
+      <c r="AG26" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="13">
         <v>46210</v>
       </c>
@@ -10473,7 +11731,7 @@
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="9" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N27" s="3"/>
@@ -10482,7 +11740,7 @@
       </c>
       <c r="P27" s="5"/>
       <c r="Q27" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R27" s="3"/>
@@ -10491,7 +11749,7 @@
       </c>
       <c r="T27" s="5"/>
       <c r="U27" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="V27" s="3"/>
@@ -10500,7 +11758,7 @@
       </c>
       <c r="X27" s="5"/>
       <c r="Y27" s="9" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Z27" s="3"/>
@@ -10509,22 +11767,31 @@
       </c>
       <c r="AB27" s="5"/>
       <c r="AC27" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AD27" s="3"/>
+      <c r="AE27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="5"/>
+      <c r="AG27" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="75" t="s">
         <v>77</v>
       </c>
       <c r="C28" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="104" t="s">
+      <c r="D28" s="123" t="s">
         <v>120</v>
       </c>
-      <c r="E28" s="105"/>
-      <c r="F28" s="106"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="125"/>
       <c r="G28" s="72" t="s">
         <v>7</v>
       </c>
@@ -10550,8 +11817,12 @@
       <c r="AA28" s="51"/>
       <c r="AB28" s="51"/>
       <c r="AC28" s="52"/>
-    </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD28" s="83"/>
+      <c r="AE28" s="84"/>
+      <c r="AF28" s="84"/>
+      <c r="AG28" s="85"/>
+    </row>
+    <row r="29" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" s="25">
         <v>46212</v>
       </c>
@@ -10613,8 +11884,17 @@
         <f>IF(ISBLANK($I29)=TRUE,"",IF(SIGN(Z29-AB29)=SIGN($G29-$I29),1,0)+IF(Z29=$G29,IF(AB29=$I29,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD29" s="27"/>
+      <c r="AE29" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF29" s="29"/>
+      <c r="AG29" s="11" t="str">
+        <f>IF(ISBLANK($I29)=TRUE,"",IF(SIGN(AD29-AF29)=SIGN($G29-$I29),1,0)+IF(AD29=$G29,IF(AF29=$I29,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B30" s="12">
         <v>46213</v>
       </c>
@@ -10637,7 +11917,7 @@
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="9" t="str">
-        <f t="shared" ref="M30:M32" si="17">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(J30-L30)=SIGN($G30-$I30),1,0)+IF(J30=$G30,IF(L30=$I30,2,0),0))</f>
+        <f t="shared" ref="M30:M32" si="20">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(J30-L30)=SIGN($G30-$I30),1,0)+IF(J30=$G30,IF(L30=$I30,2,0),0))</f>
         <v/>
       </c>
       <c r="N30" s="3"/>
@@ -10646,7 +11926,7 @@
       </c>
       <c r="P30" s="5"/>
       <c r="Q30" s="9" t="str">
-        <f t="shared" ref="Q30:Q32" si="18">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(N30-P30)=SIGN($G30-$I30),1,0)+IF(N30=$G30,IF(P30=$I30,2,0),0))</f>
+        <f t="shared" ref="Q30:Q32" si="21">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(N30-P30)=SIGN($G30-$I30),1,0)+IF(N30=$G30,IF(P30=$I30,2,0),0))</f>
         <v/>
       </c>
       <c r="R30" s="3"/>
@@ -10655,7 +11935,7 @@
       </c>
       <c r="T30" s="5"/>
       <c r="U30" s="9" t="str">
-        <f t="shared" ref="U30:U32" si="19">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(R30-T30)=SIGN($G30-$I30),1,0)+IF(R30=$G30,IF(T30=$I30,2,0),0))</f>
+        <f t="shared" ref="U30:U32" si="22">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(R30-T30)=SIGN($G30-$I30),1,0)+IF(R30=$G30,IF(T30=$I30,2,0),0))</f>
         <v/>
       </c>
       <c r="V30" s="3"/>
@@ -10664,7 +11944,7 @@
       </c>
       <c r="X30" s="5"/>
       <c r="Y30" s="9" t="str">
-        <f t="shared" ref="Y30:Y32" si="20">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(V30-X30)=SIGN($G30-$I30),1,0)+IF(V30=$G30,IF(X30=$I30,2,0),0))</f>
+        <f t="shared" ref="Y30:Y32" si="23">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(V30-X30)=SIGN($G30-$I30),1,0)+IF(V30=$G30,IF(X30=$I30,2,0),0))</f>
         <v/>
       </c>
       <c r="Z30" s="3"/>
@@ -10673,11 +11953,20 @@
       </c>
       <c r="AB30" s="5"/>
       <c r="AC30" s="9" t="str">
-        <f t="shared" ref="AC30:AC32" si="21">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(Z30-AB30)=SIGN($G30-$I30),1,0)+IF(Z30=$G30,IF(AB30=$I30,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC30:AC32" si="24">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(Z30-AB30)=SIGN($G30-$I30),1,0)+IF(Z30=$G30,IF(AB30=$I30,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="5"/>
+      <c r="AG30" s="9" t="str">
+        <f t="shared" ref="AG30:AG32" si="25">IF(ISBLANK($G30)=TRUE,"",IF(SIGN(AD30-AF30)=SIGN($G30-$I30),1,0)+IF(AD30=$G30,IF(AF30=$I30,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B31" s="12">
         <v>46214</v>
       </c>
@@ -10700,7 +11989,7 @@
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="N31" s="3"/>
@@ -10709,7 +11998,7 @@
       </c>
       <c r="P31" s="5"/>
       <c r="Q31" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R31" s="3"/>
@@ -10718,7 +12007,7 @@
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="9" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="V31" s="3"/>
@@ -10727,7 +12016,7 @@
       </c>
       <c r="X31" s="5"/>
       <c r="Y31" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Z31" s="3"/>
@@ -10736,11 +12025,20 @@
       </c>
       <c r="AB31" s="5"/>
       <c r="AC31" s="9" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AD31" s="3"/>
+      <c r="AE31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="5"/>
+      <c r="AG31" s="9" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="12">
         <v>46215</v>
       </c>
@@ -10763,7 +12061,7 @@
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="N32" s="3"/>
@@ -10772,7 +12070,7 @@
       </c>
       <c r="P32" s="5"/>
       <c r="Q32" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R32" s="3"/>
@@ -10781,7 +12079,7 @@
       </c>
       <c r="T32" s="5"/>
       <c r="U32" s="9" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="V32" s="3"/>
@@ -10790,7 +12088,7 @@
       </c>
       <c r="X32" s="5"/>
       <c r="Y32" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Z32" s="3"/>
@@ -10799,22 +12097,31 @@
       </c>
       <c r="AB32" s="5"/>
       <c r="AC32" s="9" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AD32" s="3"/>
+      <c r="AE32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="5"/>
+      <c r="AG32" s="9" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="75" t="s">
         <v>77</v>
       </c>
       <c r="C33" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="D33" s="104" t="s">
+      <c r="D33" s="123" t="s">
         <v>121</v>
       </c>
-      <c r="E33" s="105"/>
-      <c r="F33" s="106"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="125"/>
       <c r="G33" s="72" t="s">
         <v>7</v>
       </c>
@@ -10840,8 +12147,12 @@
       <c r="AA33" s="51"/>
       <c r="AB33" s="51"/>
       <c r="AC33" s="52"/>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD33" s="83"/>
+      <c r="AE33" s="84"/>
+      <c r="AF33" s="84"/>
+      <c r="AG33" s="85"/>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B34" s="25">
         <v>46217</v>
       </c>
@@ -10903,8 +12214,17 @@
         <f>IF(ISBLANK($I34)=TRUE,"",IF(SIGN(Z34-AB34)=SIGN($G34-$I34),1,0)+IF(Z34=$G34,IF(AB34=$I34,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="35" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD34" s="27"/>
+      <c r="AE34" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="29"/>
+      <c r="AG34" s="11" t="str">
+        <f>IF(ISBLANK($I34)=TRUE,"",IF(SIGN(AD34-AF34)=SIGN($G34-$I34),1,0)+IF(AD34=$G34,IF(AF34=$I34,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="12">
         <v>46218</v>
       </c>
@@ -10927,7 +12247,7 @@
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="9" t="str">
-        <f t="shared" ref="M35" si="22">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(J35-L35)=SIGN($G35-$I35),1,0)+IF(J35=$G35,IF(L35=$I35,2,0),0))</f>
+        <f t="shared" ref="M35" si="26">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(J35-L35)=SIGN($G35-$I35),1,0)+IF(J35=$G35,IF(L35=$I35,2,0),0))</f>
         <v/>
       </c>
       <c r="N35" s="3"/>
@@ -10936,7 +12256,7 @@
       </c>
       <c r="P35" s="5"/>
       <c r="Q35" s="9" t="str">
-        <f t="shared" ref="Q35" si="23">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(N35-P35)=SIGN($G35-$I35),1,0)+IF(N35=$G35,IF(P35=$I35,2,0),0))</f>
+        <f t="shared" ref="Q35" si="27">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(N35-P35)=SIGN($G35-$I35),1,0)+IF(N35=$G35,IF(P35=$I35,2,0),0))</f>
         <v/>
       </c>
       <c r="R35" s="3"/>
@@ -10945,7 +12265,7 @@
       </c>
       <c r="T35" s="5"/>
       <c r="U35" s="9" t="str">
-        <f t="shared" ref="U35" si="24">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(R35-T35)=SIGN($G35-$I35),1,0)+IF(R35=$G35,IF(T35=$I35,2,0),0))</f>
+        <f t="shared" ref="U35" si="28">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(R35-T35)=SIGN($G35-$I35),1,0)+IF(R35=$G35,IF(T35=$I35,2,0),0))</f>
         <v/>
       </c>
       <c r="V35" s="3"/>
@@ -10954,7 +12274,7 @@
       </c>
       <c r="X35" s="5"/>
       <c r="Y35" s="9" t="str">
-        <f t="shared" ref="Y35" si="25">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(V35-X35)=SIGN($G35-$I35),1,0)+IF(V35=$G35,IF(X35=$I35,2,0),0))</f>
+        <f t="shared" ref="Y35" si="29">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(V35-X35)=SIGN($G35-$I35),1,0)+IF(V35=$G35,IF(X35=$I35,2,0),0))</f>
         <v/>
       </c>
       <c r="Z35" s="3"/>
@@ -10963,22 +12283,31 @@
       </c>
       <c r="AB35" s="5"/>
       <c r="AC35" s="9" t="str">
-        <f t="shared" ref="AC35" si="26">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(Z35-AB35)=SIGN($G35-$I35),1,0)+IF(Z35=$G35,IF(AB35=$I35,2,0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="AC35" si="30">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(Z35-AB35)=SIGN($G35-$I35),1,0)+IF(Z35=$G35,IF(AB35=$I35,2,0),0))</f>
+        <v/>
+      </c>
+      <c r="AD35" s="3"/>
+      <c r="AE35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="5"/>
+      <c r="AG35" s="9" t="str">
+        <f t="shared" ref="AG35" si="31">IF(ISBLANK($G35)=TRUE,"",IF(SIGN(AD35-AF35)=SIGN($G35-$I35),1,0)+IF(AD35=$G35,IF(AF35=$I35,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="75" t="s">
         <v>77</v>
       </c>
       <c r="C36" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="D36" s="104" t="s">
+      <c r="D36" s="123" t="s">
         <v>122</v>
       </c>
-      <c r="E36" s="105"/>
-      <c r="F36" s="106"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="125"/>
       <c r="G36" s="72" t="s">
         <v>7</v>
       </c>
@@ -11004,8 +12333,12 @@
       <c r="AA36" s="51"/>
       <c r="AB36" s="51"/>
       <c r="AC36" s="52"/>
-    </row>
-    <row r="37" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD36" s="83"/>
+      <c r="AE36" s="84"/>
+      <c r="AF36" s="84"/>
+      <c r="AG36" s="85"/>
+    </row>
+    <row r="37" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="25">
         <v>46221</v>
       </c>
@@ -11067,19 +12400,28 @@
         <f>IF(ISBLANK($I37)=TRUE,"",IF(SIGN(Z37-AB37)=SIGN($G37-$I37),1,0)+IF(Z37=$G37,IF(AB37=$I37,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="38" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD37" s="27"/>
+      <c r="AE37" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="29"/>
+      <c r="AG37" s="11" t="str">
+        <f>IF(ISBLANK($I37)=TRUE,"",IF(SIGN(AD37-AF37)=SIGN($G37-$I37),1,0)+IF(AD37=$G37,IF(AF37=$I37,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="75" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="104" t="s">
+      <c r="D38" s="123" t="s">
         <v>123</v>
       </c>
-      <c r="E38" s="105"/>
-      <c r="F38" s="106"/>
+      <c r="E38" s="124"/>
+      <c r="F38" s="125"/>
       <c r="G38" s="72" t="s">
         <v>7</v>
       </c>
@@ -11105,8 +12447,12 @@
       <c r="AA38" s="51"/>
       <c r="AB38" s="51"/>
       <c r="AC38" s="52"/>
-    </row>
-    <row r="39" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD38" s="83"/>
+      <c r="AE38" s="84"/>
+      <c r="AF38" s="84"/>
+      <c r="AG38" s="85"/>
+    </row>
+    <row r="39" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="25">
         <v>46222</v>
       </c>
@@ -11168,116 +12514,131 @@
         <f>IF(ISBLANK($I39)=TRUE,"",IF(SIGN(Z39-AB39)=SIGN($G39-$I39),1,0)+IF(Z39=$G39,IF(AB39=$I39,2,0),0))</f>
         <v/>
       </c>
-    </row>
-    <row r="40" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="86" t="s">
+      <c r="AD39" s="27"/>
+      <c r="AE39" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="29"/>
+      <c r="AG39" s="11" t="str">
+        <f>IF(ISBLANK($I39)=TRUE,"",IF(SIGN(AD39-AF39)=SIGN($G39-$I39),1,0)+IF(AD39=$G39,IF(AF39=$I39,2,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="105" t="s">
         <v>130</v>
       </c>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="87"/>
-      <c r="G40" s="87"/>
-      <c r="H40" s="87"/>
-      <c r="I40" s="88"/>
-      <c r="J40" s="89">
+      <c r="C40" s="106"/>
+      <c r="D40" s="106"/>
+      <c r="E40" s="106"/>
+      <c r="F40" s="106"/>
+      <c r="G40" s="106"/>
+      <c r="H40" s="106"/>
+      <c r="I40" s="107"/>
+      <c r="J40" s="108">
         <f>SUM(M3:M39)</f>
         <v>0</v>
       </c>
-      <c r="K40" s="90"/>
-      <c r="L40" s="90"/>
-      <c r="M40" s="91"/>
-      <c r="N40" s="92">
+      <c r="K40" s="109"/>
+      <c r="L40" s="109"/>
+      <c r="M40" s="110"/>
+      <c r="N40" s="111">
         <f>SUM(Q3:Q39)</f>
         <v>0</v>
       </c>
-      <c r="O40" s="93"/>
-      <c r="P40" s="93"/>
-      <c r="Q40" s="94"/>
-      <c r="R40" s="98">
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="113"/>
+      <c r="R40" s="117">
         <f>SUM(U3:U39)</f>
         <v>0</v>
       </c>
-      <c r="S40" s="99"/>
-      <c r="T40" s="99"/>
-      <c r="U40" s="100"/>
-      <c r="V40" s="101">
+      <c r="S40" s="118"/>
+      <c r="T40" s="118"/>
+      <c r="U40" s="119"/>
+      <c r="V40" s="120">
         <f>SUM(Y3:Y39)</f>
         <v>0</v>
       </c>
-      <c r="W40" s="102"/>
-      <c r="X40" s="102"/>
-      <c r="Y40" s="103"/>
-      <c r="Z40" s="95">
+      <c r="W40" s="121"/>
+      <c r="X40" s="121"/>
+      <c r="Y40" s="122"/>
+      <c r="Z40" s="114">
         <f>SUM(AC3:AC39)</f>
         <v>0</v>
       </c>
-      <c r="AA40" s="96"/>
-      <c r="AB40" s="96"/>
-      <c r="AC40" s="97"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AA40" s="115"/>
+      <c r="AB40" s="115"/>
+      <c r="AC40" s="116"/>
+      <c r="AD40" s="99">
+        <f>SUM(AG3:AG39)</f>
+        <v>0</v>
+      </c>
+      <c r="AE40" s="100"/>
+      <c r="AF40" s="100"/>
+      <c r="AG40" s="101"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E41" s="47"/>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E42" s="47"/>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E43" s="47"/>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E44" s="47"/>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E45" s="47"/>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E46" s="47"/>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E47" s="47"/>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.25">
       <c r="E48" s="47"/>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E49" s="47"/>
     </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E50" s="47"/>
     </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E51" s="47"/>
     </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E52" s="47"/>
     </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E53" s="47"/>
     </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E54" s="47"/>
     </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E55" s="47"/>
     </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E56" s="47"/>
     </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E57" s="47"/>
     </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E58" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="Z2:AC2"/>
-    <mergeCell ref="Z40:AC40"/>
-    <mergeCell ref="R2:U2"/>
+  <mergeCells count="19">
     <mergeCell ref="R40:U40"/>
     <mergeCell ref="V2:Y2"/>
     <mergeCell ref="V40:Y40"/>
+    <mergeCell ref="AD2:AG2"/>
+    <mergeCell ref="AD40:AG40"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:Q2"/>
@@ -11289,8 +12650,11 @@
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="J40:M40"/>
     <mergeCell ref="D36:F36"/>
+    <mergeCell ref="Z2:AC2"/>
+    <mergeCell ref="Z40:AC40"/>
+    <mergeCell ref="R2:U2"/>
   </mergeCells>
-  <conditionalFormatting sqref="M3:M18 Q3:Q18 U3:U18 Y3:Y18 AC3:AC18">
+  <conditionalFormatting sqref="M3:M18 Q3:Q18 U3:U18 Y3:Y18 AC3:AC18 AG3:AG18">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11300,7 +12664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M20:M27 Q20:Q27 U20:U27 Y20:Y27 AC20:AC27">
+  <conditionalFormatting sqref="M20:M27 Q20:Q27 U20:U27 Y20:Y27 AC20:AC27 AG20:AG27">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11310,7 +12674,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M29:M32 Q29:Q32 U29:U32 Y29:Y32 AC29:AC32">
+  <conditionalFormatting sqref="M29:M32 Q29:Q32 U29:U32 Y29:Y32 AC29:AC32 AG29:AG32">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11320,7 +12684,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M34:M35 Q34:Q35 U34:U35 Y34:Y35 AC34:AC35">
+  <conditionalFormatting sqref="M34:M35 Q34:Q35 U34:U35 Y34:Y35 AC34:AC35 AG34:AG35">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11330,8 +12694,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M37 Q37 U37 Y37 AC37">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="M39 Q39 U39 Y39 AC39 AG39">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="3"/>
@@ -11340,8 +12704,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M39 Q39 U39 Y39 AC39">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="Q37 M37 U37 Y37 AC37 AG37">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="3"/>
@@ -11356,61 +12720,67 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC74864-1BC4-4CC2-A75F-01ADCFA0670D}">
-  <dimension ref="B1:P44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:R44"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="47" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="47" customWidth="1"/>
-    <col min="3" max="3" width="56.109375" style="47" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.109375" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5546875" style="47" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.5703125" style="47" customWidth="1"/>
+    <col min="3" max="3" width="56.140625" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.140625" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" style="47" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" style="47" customWidth="1"/>
-    <col min="8" max="8" width="3.6640625" style="47" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" style="47" customWidth="1"/>
-    <col min="10" max="10" width="3.6640625" style="47" customWidth="1"/>
-    <col min="11" max="11" width="17.109375" style="47" customWidth="1"/>
-    <col min="12" max="12" width="3.6640625" style="47" customWidth="1"/>
-    <col min="13" max="13" width="17.109375" style="47" customWidth="1"/>
-    <col min="14" max="14" width="3.6640625" style="47" customWidth="1"/>
-    <col min="15" max="15" width="17.109375" style="47" customWidth="1"/>
-    <col min="16" max="16" width="3.6640625" style="47" customWidth="1"/>
-    <col min="17" max="16384" width="11.44140625" style="47"/>
+    <col min="7" max="7" width="17.140625" style="47" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="47" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" style="47" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" style="47" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" style="47" customWidth="1"/>
+    <col min="12" max="12" width="3.7109375" style="47" customWidth="1"/>
+    <col min="13" max="13" width="17.140625" style="47" customWidth="1"/>
+    <col min="14" max="14" width="3.7109375" style="47" customWidth="1"/>
+    <col min="15" max="15" width="17.140625" style="47" customWidth="1"/>
+    <col min="16" max="16" width="3.7109375" style="47" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" style="47" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" style="47" customWidth="1"/>
+    <col min="19" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="83" t="s">
+    <row r="1" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="83" t="s">
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="102" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="85"/>
-      <c r="G2" s="89" t="s">
+      <c r="F2" s="104"/>
+      <c r="G2" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="91"/>
-      <c r="I2" s="114" t="s">
+      <c r="H2" s="110"/>
+      <c r="I2" s="127" t="s">
         <v>139</v>
       </c>
-      <c r="J2" s="115"/>
-      <c r="K2" s="98" t="s">
+      <c r="J2" s="128"/>
+      <c r="K2" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="L2" s="100"/>
-      <c r="M2" s="101" t="s">
+      <c r="L2" s="119"/>
+      <c r="M2" s="120" t="s">
         <v>140</v>
       </c>
-      <c r="N2" s="103"/>
-      <c r="O2" s="95" t="s">
+      <c r="N2" s="122"/>
+      <c r="O2" s="114" t="s">
         <v>138</v>
       </c>
-      <c r="P2" s="97"/>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="P2" s="116"/>
+      <c r="Q2" s="99" t="s">
+        <v>167</v>
+      </c>
+      <c r="R2" s="101"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" s="37" t="s">
         <v>85</v>
       </c>
@@ -11420,8 +12790,8 @@
       <c r="D3" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="112"/>
-      <c r="F3" s="113"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="94"/>
       <c r="G3" s="17" t="s">
         <v>44</v>
       </c>
@@ -11455,8 +12825,15 @@
         <f>IF(ISBLANK($E3)=TRUE,"",IF($E3=O3,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q3" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="9" t="str">
+        <f>IF(ISBLANK($E3)=TRUE,"",IF($E3=Q3,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B4" s="38" t="s">
         <v>86</v>
       </c>
@@ -11466,8 +12843,8 @@
       <c r="D4" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="107"/>
-      <c r="F4" s="108"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="96"/>
       <c r="G4" s="18" t="s">
         <v>116</v>
       </c>
@@ -11501,8 +12878,15 @@
         <f>IF(ISBLANK($E4)=TRUE,"",IF($E4=O4,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q4" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="R4" s="9" t="str">
+        <f>IF(ISBLANK($E4)=TRUE,"",IF($E4=Q4,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="38" t="s">
         <v>87</v>
       </c>
@@ -11512,8 +12896,8 @@
       <c r="D5" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="107"/>
-      <c r="F5" s="108"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="96"/>
       <c r="G5" s="18" t="s">
         <v>116</v>
       </c>
@@ -11547,8 +12931,15 @@
         <f>IF(ISBLANK($E5)=TRUE,"",IF($E5=O5,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q5" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="R5" s="9" t="str">
+        <f>IF(ISBLANK($E5)=TRUE,"",IF($E5=Q5,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B6" s="38" t="s">
         <v>88</v>
       </c>
@@ -11558,8 +12949,8 @@
       <c r="D6" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="107"/>
-      <c r="F6" s="108"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="96"/>
       <c r="G6" s="18" t="s">
         <v>117</v>
       </c>
@@ -11593,8 +12984,15 @@
         <f>IF(ISBLANK($E6)=TRUE,"",IF($E6=O6,3,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="7" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q6" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="R6" s="9" t="str">
+        <f>IF(ISBLANK($E6)=TRUE,"",IF($E6=Q6,3,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="38" t="s">
         <v>89</v>
       </c>
@@ -11604,8 +13002,8 @@
       <c r="D7" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="107"/>
-      <c r="F7" s="108"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="96"/>
       <c r="G7" s="40">
         <v>241</v>
       </c>
@@ -11639,8 +13037,15 @@
         <f>IF(ISBLANK($E7)=TRUE,"",IF($E7=O7,2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q7" s="40">
+        <v>333</v>
+      </c>
+      <c r="R7" s="9" t="str">
+        <f>IF(ISBLANK($E7)=TRUE,"",IF($E7=Q7,2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="38"/>
       <c r="C8" s="21"/>
       <c r="D8" s="15"/>
@@ -11661,8 +13066,10 @@
       <c r="N8" s="9"/>
       <c r="O8" s="40"/>
       <c r="P8" s="9"/>
-    </row>
-    <row r="9" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q8" s="40"/>
+      <c r="R8" s="9"/>
+    </row>
+    <row r="9" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="38"/>
       <c r="C9" s="21"/>
       <c r="D9" s="15"/>
@@ -11683,8 +13090,10 @@
       <c r="N9" s="9"/>
       <c r="O9" s="40"/>
       <c r="P9" s="9"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q9" s="40"/>
+      <c r="R9" s="9"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="38" t="s">
         <v>90</v>
       </c>
@@ -11694,8 +13103,8 @@
       <c r="D10" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="109"/>
-      <c r="F10" s="108"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="96"/>
       <c r="G10" s="23">
         <v>4.0509259259259258E-4</v>
       </c>
@@ -11729,8 +13138,15 @@
         <f>IF(ISBLANK($E10),"",IF(ABS($E10-O10)&lt;TIME(0,0,16),2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q10" s="23">
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="R10" s="9" t="str">
+        <f>IF(ISBLANK($E10),"",IF(ABS($E10-Q10)&lt;TIME(0,0,16),2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="38" t="s">
         <v>91</v>
       </c>
@@ -11740,8 +13156,8 @@
       <c r="D11" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E11" s="107"/>
-      <c r="F11" s="108"/>
+      <c r="E11" s="95"/>
+      <c r="F11" s="96"/>
       <c r="G11" s="18" t="s">
         <v>31</v>
       </c>
@@ -11775,13 +13191,20 @@
         <f>IF(ISBLANK($E11)=TRUE,"",IF(ISNUMBER(SEARCH(O11,$E11)),2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q11" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" s="9" t="str">
+        <f>IF(ISBLANK($E11)=TRUE,"",IF(ISNUMBER(SEARCH(Q11,$E11)),2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="38"/>
       <c r="C12" s="21"/>
       <c r="D12" s="15"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="108"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="96"/>
       <c r="G12" s="18" t="s">
         <v>54</v>
       </c>
@@ -11815,8 +13238,15 @@
         <f>IF(ISBLANK($E11)=TRUE,"",IF(ISNUMBER(SEARCH(O12,$E11)),2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q12" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="R12" s="9" t="str">
+        <f>IF(ISBLANK($E11)=TRUE,"",IF(ISNUMBER(SEARCH(Q12,$E11)),2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="38" t="s">
         <v>92</v>
       </c>
@@ -11826,8 +13256,8 @@
       <c r="D13" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="107"/>
-      <c r="F13" s="108"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="96"/>
       <c r="G13" s="18" t="s">
         <v>142</v>
       </c>
@@ -11861,13 +13291,20 @@
         <f>IF(ISBLANK($E13)=TRUE,"",IF(ISNUMBER(SEARCH(O13,$E13)),2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q13" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="R13" s="9" t="str">
+        <f>IF(ISBLANK($E13)=TRUE,"",IF(ISNUMBER(SEARCH(Q13,$E13)),2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="38"/>
       <c r="C14" s="21"/>
       <c r="D14" s="15"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="108"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="96"/>
       <c r="G14" s="18" t="s">
         <v>40</v>
       </c>
@@ -11901,8 +13338,15 @@
         <f>IF(ISBLANK($E13)=TRUE,"",IF(ISNUMBER(SEARCH(O14,$E13)),2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q14" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="R14" s="9" t="str">
+        <f>IF(ISBLANK($E13)=TRUE,"",IF(ISNUMBER(SEARCH(Q14,$E13)),2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="38" t="s">
         <v>93</v>
       </c>
@@ -11912,8 +13356,8 @@
       <c r="D15" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="107"/>
-      <c r="F15" s="108"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="96"/>
       <c r="G15" s="18" t="s">
         <v>151</v>
       </c>
@@ -11947,8 +13391,15 @@
         <f>IF(ISBLANK($E15)=TRUE,"",IF($E15=O15,2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="R15" s="9" t="str">
+        <f>IF(ISBLANK($E15)=TRUE,"",IF($E15=Q15,2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="38" t="s">
         <v>94</v>
       </c>
@@ -11958,8 +13409,8 @@
       <c r="D16" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="107"/>
-      <c r="F16" s="108"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="96"/>
       <c r="G16" s="18" t="s">
         <v>142</v>
       </c>
@@ -11993,8 +13444,15 @@
         <f>IF(ISBLANK($E16)=TRUE,"",IF($E16=O16,2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q16" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="R16" s="9" t="str">
+        <f>IF(ISBLANK($E16)=TRUE,"",IF($E16=Q16,2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="38" t="s">
         <v>95</v>
       </c>
@@ -12004,8 +13462,8 @@
       <c r="D17" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="107"/>
-      <c r="F17" s="108"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="96"/>
       <c r="G17" s="18" t="s">
         <v>143</v>
       </c>
@@ -12039,8 +13497,15 @@
         <f>IF(ISBLANK($E17)=TRUE,"",IF($E17=O17,4,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q17" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="R17" s="9" t="str">
+        <f>IF(ISBLANK($E17)=TRUE,"",IF($E17=Q17,4,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="38" t="s">
         <v>96</v>
       </c>
@@ -12050,8 +13515,8 @@
       <c r="D18" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="107"/>
-      <c r="F18" s="108"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="96"/>
       <c r="G18" s="18" t="s">
         <v>32</v>
       </c>
@@ -12085,8 +13550,15 @@
         <f>IF(ISBLANK($E18)=TRUE,"",IF($E18=O18,2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q18" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" s="9" t="str">
+        <f>IF(ISBLANK($E18)=TRUE,"",IF($E18=Q18,2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="38" t="s">
         <v>97</v>
       </c>
@@ -12096,8 +13568,8 @@
       <c r="D19" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="107"/>
-      <c r="F19" s="108"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="96"/>
       <c r="G19" s="18" t="s">
         <v>144</v>
       </c>
@@ -12131,8 +13603,15 @@
         <f>IF(ISBLANK($E19)=TRUE,"",IF($E19=O19,1,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q19" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="R19" s="9" t="str">
+        <f>IF(ISBLANK($E19)=TRUE,"",IF($E19=Q19,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="38" t="s">
         <v>98</v>
       </c>
@@ -12142,8 +13621,8 @@
       <c r="D20" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="107"/>
-      <c r="F20" s="108"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="96"/>
       <c r="G20" s="18" t="s">
         <v>20</v>
       </c>
@@ -12177,8 +13656,15 @@
         <f>IF(ISBLANK($E20)=TRUE,"",IF($E20=O20,2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q20" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" s="9" t="str">
+        <f>IF(ISBLANK($E20)=TRUE,"",IF($E20=Q20,2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="38" t="s">
         <v>99</v>
       </c>
@@ -12188,8 +13674,8 @@
       <c r="D21" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="107"/>
-      <c r="F21" s="108"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="96"/>
       <c r="G21" s="18" t="s">
         <v>145</v>
       </c>
@@ -12223,8 +13709,15 @@
         <f>IF(ISBLANK($E21)=TRUE,"",IF(ISNUMBER(SEARCH(O21,$E21)),3,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q21" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="R21" s="9" t="str">
+        <f>IF(ISBLANK($E21)=TRUE,"",IF(ISNUMBER(SEARCH(Q21,$E21)),3,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="38" t="s">
         <v>100</v>
       </c>
@@ -12234,8 +13727,8 @@
       <c r="D22" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="107"/>
-      <c r="F22" s="108"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="96"/>
       <c r="G22" s="18" t="s">
         <v>146</v>
       </c>
@@ -12269,8 +13762,15 @@
         <f>IF(ISBLANK($E22)=TRUE,"",IF(ISNUMBER(SEARCH(O22,$E22)),1,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q22" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="R22" s="9" t="str">
+        <f>IF(ISBLANK($E22)=TRUE,"",IF(ISNUMBER(SEARCH(Q22,$E22)),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="39" t="s">
         <v>160</v>
       </c>
@@ -12280,8 +13780,8 @@
       <c r="D23" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="110"/>
-      <c r="F23" s="111"/>
+      <c r="E23" s="97"/>
+      <c r="F23" s="98"/>
       <c r="G23" s="19" t="s">
         <v>161</v>
       </c>
@@ -12315,15 +13815,20 @@
         <f>IF(ISBLANK($E23)=TRUE,"",IF($E23=O23,2,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="83" t="s">
+      <c r="Q23" s="19"/>
+      <c r="R23" s="10" t="str">
+        <f>IF(ISBLANK($E23)=TRUE,"",IF($E23=Q23,2,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="102" t="s">
         <v>131</v>
       </c>
-      <c r="C24" s="84"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="85"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="104"/>
       <c r="G24" s="34"/>
       <c r="H24" s="35"/>
       <c r="I24" s="44"/>
@@ -12334,15 +13839,17 @@
       <c r="N24" s="54"/>
       <c r="O24" s="50"/>
       <c r="P24" s="51"/>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q24" s="83"/>
+      <c r="R24" s="86"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="37" t="s">
         <v>85</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="14"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="113"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="94"/>
       <c r="G25" s="17"/>
       <c r="H25" s="9" t="str">
         <f>IF(ISBLANK($E25)=TRUE,"",IF($E25=G25,5,0))</f>
@@ -12368,15 +13875,20 @@
         <f>IF(ISBLANK($E25)=TRUE,"",IF($E25=O25,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q25" s="17"/>
+      <c r="R25" s="9" t="str">
+        <f>IF(ISBLANK($E25)=TRUE,"",IF($E25=Q25,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="38" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="21"/>
       <c r="D26" s="15"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="108"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="96"/>
       <c r="G26" s="18"/>
       <c r="H26" s="9" t="str">
         <f>IF(ISBLANK($E26)=TRUE,"",IF($E26=G26,5,0))</f>
@@ -12402,15 +13914,20 @@
         <f>IF(ISBLANK($E26)=TRUE,"",IF($E26=O26,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q26" s="18"/>
+      <c r="R26" s="9" t="str">
+        <f>IF(ISBLANK($E26)=TRUE,"",IF($E26=Q26,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="38" t="s">
         <v>87</v>
       </c>
       <c r="C27" s="21"/>
       <c r="D27" s="15"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="111"/>
+      <c r="E27" s="97"/>
+      <c r="F27" s="98"/>
       <c r="G27" s="18"/>
       <c r="H27" s="9" t="str">
         <f>IF(ISBLANK($E27)=TRUE,"",IF($E27=G27,5,0))</f>
@@ -12436,15 +13953,20 @@
         <f>IF(ISBLANK($E27)=TRUE,"",IF($E27=O27,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="83" t="s">
+      <c r="Q27" s="18"/>
+      <c r="R27" s="9" t="str">
+        <f>IF(ISBLANK($E27)=TRUE,"",IF($E27=Q27,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="102" t="s">
         <v>132</v>
       </c>
-      <c r="C28" s="84"/>
-      <c r="D28" s="85"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="85"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="104"/>
       <c r="G28" s="34"/>
       <c r="H28" s="35"/>
       <c r="I28" s="44"/>
@@ -12455,15 +13977,17 @@
       <c r="N28" s="54"/>
       <c r="O28" s="50"/>
       <c r="P28" s="51"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q28" s="87"/>
+      <c r="R28" s="86"/>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="37" t="s">
         <v>85</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="14"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="113"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="94"/>
       <c r="G29" s="17"/>
       <c r="H29" s="11" t="str">
         <f>IF(ISBLANK($E29)=TRUE,"",IF($E29=G29,5,0))</f>
@@ -12489,15 +14013,20 @@
         <f>IF(ISBLANK($E29)=TRUE,"",IF($E29=O29,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q29" s="17"/>
+      <c r="R29" s="11" t="str">
+        <f>IF(ISBLANK($E29)=TRUE,"",IF($E29=Q29,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="38" t="s">
         <v>86</v>
       </c>
       <c r="C30" s="21"/>
       <c r="D30" s="15"/>
-      <c r="E30" s="107"/>
-      <c r="F30" s="108"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="96"/>
       <c r="G30" s="18"/>
       <c r="H30" s="9" t="str">
         <f>IF(ISBLANK($E30)=TRUE,"",IF($E30=G30,5,0))</f>
@@ -12523,15 +14052,20 @@
         <f>IF(ISBLANK($E30)=TRUE,"",IF($E30=O30,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q30" s="18"/>
+      <c r="R30" s="9" t="str">
+        <f>IF(ISBLANK($E30)=TRUE,"",IF($E30=Q30,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="38" t="s">
         <v>87</v>
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="15"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="111"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="98"/>
       <c r="G31" s="18"/>
       <c r="H31" s="9" t="str">
         <f>IF(ISBLANK($E31)=TRUE,"",IF($E31=G31,5,0))</f>
@@ -12557,15 +14091,20 @@
         <f>IF(ISBLANK($E31)=TRUE,"",IF($E31=O31,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="83" t="s">
+      <c r="Q31" s="18"/>
+      <c r="R31" s="9" t="str">
+        <f>IF(ISBLANK($E31)=TRUE,"",IF($E31=Q31,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="102" t="s">
         <v>133</v>
       </c>
-      <c r="C32" s="84"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="85"/>
+      <c r="C32" s="103"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="104"/>
       <c r="G32" s="34"/>
       <c r="H32" s="35"/>
       <c r="I32" s="44"/>
@@ -12576,15 +14115,17 @@
       <c r="N32" s="54"/>
       <c r="O32" s="50"/>
       <c r="P32" s="51"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q32" s="87"/>
+      <c r="R32" s="86"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="37" t="s">
         <v>85</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="14"/>
-      <c r="E33" s="112"/>
-      <c r="F33" s="113"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="94"/>
       <c r="G33" s="17"/>
       <c r="H33" s="11" t="str">
         <f>IF(ISBLANK($E33)=TRUE,"",IF($E33=G33,5,0))</f>
@@ -12610,15 +14151,20 @@
         <f>IF(ISBLANK($E33)=TRUE,"",IF($E33=O33,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q33" s="17"/>
+      <c r="R33" s="11" t="str">
+        <f>IF(ISBLANK($E33)=TRUE,"",IF($E33=Q33,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="38" t="s">
         <v>86</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="15"/>
-      <c r="E34" s="107"/>
-      <c r="F34" s="108"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="96"/>
       <c r="G34" s="18"/>
       <c r="H34" s="9" t="str">
         <f>IF(ISBLANK($E34)=TRUE,"",IF($E34=G34,5,0))</f>
@@ -12644,15 +14190,20 @@
         <f>IF(ISBLANK($E34)=TRUE,"",IF($E34=O34,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q34" s="18"/>
+      <c r="R34" s="9" t="str">
+        <f>IF(ISBLANK($E34)=TRUE,"",IF($E34=Q34,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="38" t="s">
         <v>87</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="15"/>
-      <c r="E35" s="110"/>
-      <c r="F35" s="111"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="98"/>
       <c r="G35" s="18"/>
       <c r="H35" s="9" t="str">
         <f>IF(ISBLANK($E35)=TRUE,"",IF($E35=G35,5,0))</f>
@@ -12678,15 +14229,20 @@
         <f>IF(ISBLANK($E35)=TRUE,"",IF($E35=O35,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="83" t="s">
+      <c r="Q35" s="18"/>
+      <c r="R35" s="9" t="str">
+        <f>IF(ISBLANK($E35)=TRUE,"",IF($E35=Q35,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="102" t="s">
         <v>134</v>
       </c>
-      <c r="C36" s="84"/>
-      <c r="D36" s="85"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="85"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="104"/>
+      <c r="E36" s="102"/>
+      <c r="F36" s="104"/>
       <c r="G36" s="34"/>
       <c r="H36" s="35"/>
       <c r="I36" s="44"/>
@@ -12697,15 +14253,17 @@
       <c r="N36" s="54"/>
       <c r="O36" s="50"/>
       <c r="P36" s="51"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q36" s="87"/>
+      <c r="R36" s="86"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="37" t="s">
         <v>85</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="14"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="113"/>
+      <c r="E37" s="93"/>
+      <c r="F37" s="94"/>
       <c r="G37" s="17"/>
       <c r="H37" s="11" t="str">
         <f>IF(ISBLANK($E37)=TRUE,"",IF($E37=G37,5,0))</f>
@@ -12731,15 +14289,20 @@
         <f>IF(ISBLANK($E37)=TRUE,"",IF($E37=O37,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q37" s="17"/>
+      <c r="R37" s="11" t="str">
+        <f>IF(ISBLANK($E37)=TRUE,"",IF($E37=Q37,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="38" t="s">
         <v>86</v>
       </c>
       <c r="C38" s="21"/>
       <c r="D38" s="15"/>
-      <c r="E38" s="107"/>
-      <c r="F38" s="108"/>
+      <c r="E38" s="95"/>
+      <c r="F38" s="96"/>
       <c r="G38" s="18"/>
       <c r="H38" s="9" t="str">
         <f>IF(ISBLANK($E38)=TRUE,"",IF($E38=G38,5,0))</f>
@@ -12765,15 +14328,20 @@
         <f>IF(ISBLANK($E38)=TRUE,"",IF($E38=O38,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q38" s="18"/>
+      <c r="R38" s="9" t="str">
+        <f>IF(ISBLANK($E38)=TRUE,"",IF($E38=Q38,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="38" t="s">
         <v>87</v>
       </c>
       <c r="C39" s="21"/>
       <c r="D39" s="15"/>
-      <c r="E39" s="110"/>
-      <c r="F39" s="111"/>
+      <c r="E39" s="97"/>
+      <c r="F39" s="98"/>
       <c r="G39" s="18"/>
       <c r="H39" s="9" t="str">
         <f>IF(ISBLANK($E39)=TRUE,"",IF($E39=G39,5,0))</f>
@@ -12799,15 +14367,20 @@
         <f>IF(ISBLANK($E39)=TRUE,"",IF($E39=O39,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="83" t="s">
+      <c r="Q39" s="18"/>
+      <c r="R39" s="9" t="str">
+        <f>IF(ISBLANK($E39)=TRUE,"",IF($E39=Q39,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="102" t="s">
         <v>135</v>
       </c>
-      <c r="C40" s="84"/>
-      <c r="D40" s="85"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="85"/>
+      <c r="C40" s="103"/>
+      <c r="D40" s="104"/>
+      <c r="E40" s="102"/>
+      <c r="F40" s="104"/>
       <c r="G40" s="34"/>
       <c r="H40" s="35"/>
       <c r="I40" s="44"/>
@@ -12818,15 +14391,17 @@
       <c r="N40" s="54"/>
       <c r="O40" s="50"/>
       <c r="P40" s="51"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q40" s="87"/>
+      <c r="R40" s="86"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="37" t="s">
         <v>85</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="14"/>
-      <c r="E41" s="112"/>
-      <c r="F41" s="113"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="94"/>
       <c r="G41" s="17"/>
       <c r="H41" s="11" t="str">
         <f>IF(ISBLANK($E41)=TRUE,"",IF($E41=G41,5,0))</f>
@@ -12852,15 +14427,20 @@
         <f>IF(ISBLANK($E41)=TRUE,"",IF($E41=O41,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="Q41" s="17"/>
+      <c r="R41" s="11" t="str">
+        <f>IF(ISBLANK($E41)=TRUE,"",IF($E41=Q41,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="38" t="s">
         <v>86</v>
       </c>
       <c r="C42" s="21"/>
       <c r="D42" s="15"/>
-      <c r="E42" s="107"/>
-      <c r="F42" s="108"/>
+      <c r="E42" s="95"/>
+      <c r="F42" s="96"/>
       <c r="G42" s="18"/>
       <c r="H42" s="9" t="str">
         <f>IF(ISBLANK($E42)=TRUE,"",IF($E42=G42,5,0))</f>
@@ -12886,15 +14466,20 @@
         <f>IF(ISBLANK($E42)=TRUE,"",IF($E42=O42,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q42" s="18"/>
+      <c r="R42" s="9" t="str">
+        <f>IF(ISBLANK($E42)=TRUE,"",IF($E42=Q42,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="39" t="s">
         <v>87</v>
       </c>
       <c r="C43" s="22"/>
       <c r="D43" s="16"/>
-      <c r="E43" s="110"/>
-      <c r="F43" s="111"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="98"/>
       <c r="G43" s="19"/>
       <c r="H43" s="10" t="str">
         <f>IF(ISBLANK($E43)=TRUE,"",IF($E43=G43,5,0))</f>
@@ -12920,43 +14505,54 @@
         <f>IF(ISBLANK($E43)=TRUE,"",IF($E43=O43,5,0))</f>
         <v/>
       </c>
-    </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="83" t="s">
+      <c r="Q43" s="19"/>
+      <c r="R43" s="10" t="str">
+        <f>IF(ISBLANK($E43)=TRUE,"",IF($E43=Q43,5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="102" t="s">
         <v>136</v>
       </c>
-      <c r="C44" s="84"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="84"/>
-      <c r="F44" s="85"/>
-      <c r="G44" s="89">
+      <c r="C44" s="103"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="108">
         <f>SUM(H3:H43)</f>
         <v>0</v>
       </c>
-      <c r="H44" s="91"/>
-      <c r="I44" s="92">
+      <c r="H44" s="110"/>
+      <c r="I44" s="111">
         <f>SUM(J3:J43)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="94"/>
-      <c r="K44" s="98">
+      <c r="J44" s="113"/>
+      <c r="K44" s="117">
         <f>SUM(L3:L43)</f>
         <v>0</v>
       </c>
-      <c r="L44" s="100"/>
-      <c r="M44" s="101">
+      <c r="L44" s="119"/>
+      <c r="M44" s="120">
         <f>SUM(N3:N43)</f>
         <v>0</v>
       </c>
-      <c r="N44" s="103"/>
-      <c r="O44" s="95">
+      <c r="N44" s="122"/>
+      <c r="O44" s="114">
         <f>SUM(P3:P43)</f>
         <v>0</v>
       </c>
-      <c r="P44" s="97"/>
+      <c r="P44" s="116"/>
+      <c r="Q44" s="99">
+        <f>SUM(R3:R43)</f>
+        <v>0</v>
+      </c>
+      <c r="R44" s="101"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="57">
+    <mergeCell ref="E11:F12"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="O44:P44"/>
     <mergeCell ref="I2:J2"/>
@@ -12965,6 +14561,7 @@
     <mergeCell ref="K44:L44"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M44:N44"/>
+    <mergeCell ref="E40:F40"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B24:D24"/>
@@ -12980,7 +14577,8 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E13:F14"/>
-    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="G44:H44"/>
     <mergeCell ref="B28:D28"/>
@@ -12995,7 +14593,8 @@
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="Q44:R44"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E7:F7"/>
@@ -13010,8 +14609,6 @@
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E24:F24"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H3:H23">
@@ -13206,7 +14803,7 @@
       <formula>LEN(TRIM(N41))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P23">
+  <conditionalFormatting sqref="P3:P23 R3:R23">
     <cfRule type="cellIs" dxfId="11" priority="12" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -13214,7 +14811,7 @@
       <formula>LEN(TRIM(P3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P25:P27">
+  <conditionalFormatting sqref="P25:P27 R25:R27">
     <cfRule type="cellIs" dxfId="9" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -13222,7 +14819,7 @@
       <formula>LEN(TRIM(P25))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P29:P31">
+  <conditionalFormatting sqref="P29:P31 R29:R31">
     <cfRule type="cellIs" dxfId="7" priority="8" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -13230,7 +14827,7 @@
       <formula>LEN(TRIM(P29))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P33:P35">
+  <conditionalFormatting sqref="P33:P35 R33:R35">
     <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -13238,7 +14835,7 @@
       <formula>LEN(TRIM(P33))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P37:P39">
+  <conditionalFormatting sqref="P37:P39 R37:R39">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -13246,7 +14843,7 @@
       <formula>LEN(TRIM(P37))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P41:P43">
+  <conditionalFormatting sqref="P41:P43 R41:R43">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
@@ -13261,21 +14858,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF1B7703-F9D8-497F-8DFC-5E802F9A84A8}">
-  <dimension ref="B1:H14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:I15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" style="47" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" style="47" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="7.109375" style="47" customWidth="1"/>
-    <col min="9" max="16384" width="11.44140625" style="47"/>
+    <col min="3" max="3" width="16.42578125" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="7.140625" style="47" customWidth="1"/>
+    <col min="10" max="16384" width="11.42578125" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="117" t="s">
+    <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="91" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="118"/>
+      <c r="C2" s="92"/>
       <c r="D2" s="56" t="s">
         <v>6</v>
       </c>
@@ -13291,12 +14888,15 @@
       <c r="H2" s="60" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="112" t="s">
+      <c r="I2" s="88" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="113"/>
+      <c r="C3" s="94"/>
       <c r="D3" s="11">
         <f>Gruppespill!J86</f>
         <v>0</v>
@@ -13317,12 +14917,16 @@
         <f>Gruppespill!Z86</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="107" t="s">
+      <c r="I3" s="11">
+        <f>Gruppespill!AD86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="95" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="108"/>
+      <c r="C4" s="96"/>
       <c r="D4" s="9">
         <f>Utslagsrunder!J40</f>
         <v>0</v>
@@ -13343,12 +14947,16 @@
         <f>Utslagsrunder!Z40</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="110" t="s">
+      <c r="I4" s="9">
+        <f>Utslagsrunder!AD40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="111"/>
+      <c r="C5" s="98"/>
       <c r="D5" s="10">
         <f>Krydderspørsmål!G44</f>
         <v>0</v>
@@ -13369,12 +14977,16 @@
         <f>Krydderspørsmål!O44</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="117" t="s">
+      <c r="I5" s="10">
+        <f>Krydderspørsmål!Q44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="91" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="118"/>
+      <c r="C6" s="92"/>
       <c r="D6" s="61">
         <f>SUM(D3:D5)</f>
         <v>0</v>
@@ -13395,12 +15007,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-    </row>
-    <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I6" s="89">
+        <f t="shared" ref="I6" si="1">SUM(I3:I5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="90"/>
+      <c r="D8" s="90"/>
+    </row>
+    <row r="9" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="79" t="s">
         <v>166</v>
       </c>
@@ -13411,60 +15027,71 @@
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="80">
         <v>1</v>
       </c>
-      <c r="C10" s="66" t="str" cm="1">
-        <f t="array" ref="C10:C14">_xlfn.SORTBY(TRANSPOSE(D2:H2),TRANSPOSE(D6:H6),-1)</f>
+      <c r="C10" s="15" t="str" cm="1">
+        <f t="array" ref="C10:C15">_xlfn.SORTBY(TRANSPOSE(D2:I2),TRANSPOSE(D6:I6),-1)</f>
         <v>Erling</v>
       </c>
-      <c r="D10" s="66" cm="1">
-        <f t="array" ref="D10:D14">_xlfn.SORTBY(TRANSPOSE(D6:H6),TRANSPOSE(D6:H6),-1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D10" s="67" cm="1">
+        <f t="array" ref="D10:D15">_xlfn.SORTBY(TRANSPOSE(D6:I6),TRANSPOSE(D6:I6),-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="81">
         <v>2</v>
       </c>
-      <c r="C11" s="67" t="str">
+      <c r="C11" s="15" t="str">
         <v>Rune</v>
       </c>
       <c r="D11" s="67">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="81">
         <v>3</v>
       </c>
-      <c r="C12" s="67" t="str">
+      <c r="C12" s="15" t="str">
         <v>Håkon</v>
       </c>
       <c r="D12" s="67">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="81">
         <v>4</v>
       </c>
-      <c r="C13" s="67" t="str">
+      <c r="C13" s="15" t="str">
         <v>Geir</v>
       </c>
       <c r="D13" s="67">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="82">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="81">
         <v>5</v>
       </c>
-      <c r="C14" s="68" t="str">
+      <c r="C14" s="15" t="str">
         <v>Tore</v>
       </c>
-      <c r="D14" s="68">
+      <c r="D14" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="82">
+        <v>6</v>
+      </c>
+      <c r="C15" s="16" t="str">
+        <v>Tor Arne</v>
+      </c>
+      <c r="D15" s="68">
         <v>0</v>
       </c>
     </row>
